--- a/FUD Database.xlsx
+++ b/FUD Database.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30527"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/a4bfe6e8f062496f/Desktop/Grid/NEW PATH - FUD/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="303" documentId="8_{30167142-7360-4562-A86A-6E0411E62A9D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{699BF877-B533-48D3-B439-B499D9E30987}"/>
+  <xr:revisionPtr revIDLastSave="390" documentId="8_{30167142-7360-4562-A86A-6E0411E62A9D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C83439E8-AF6E-4C4E-A7DC-604405E1525C}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25180" windowHeight="16140" xr2:uid="{07F1D9CF-A2D1-42AB-8E4E-EAB3AA23EDEE}"/>
   </bookViews>
@@ -17,9 +17,10 @@
     <sheet name="Others" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$F$271</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$F$282</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -43,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2074" uniqueCount="547">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2089" uniqueCount="551">
   <si>
     <t>Skill Level</t>
   </si>
@@ -1684,6 +1685,18 @@
   </si>
   <si>
     <t>Ricky Pearsall</t>
+  </si>
+  <si>
+    <t>Christian Kirk</t>
+  </si>
+  <si>
+    <t>Kyle Juszczyk</t>
+  </si>
+  <si>
+    <t>Savion Williams</t>
+  </si>
+  <si>
+    <t>Treylon Burks</t>
   </si>
 </sst>
 </file>
@@ -2078,7 +2091,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1909AEDC-558D-47FF-AACF-A1C78DAFF0D0}">
-  <dimension ref="A1:J284"/>
+  <dimension ref="A1:J282"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="14.7265625" bestFit="1" customWidth="1"/>
@@ -2258,7 +2271,7 @@
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B9" t="s">
         <v>52</v>
@@ -2367,7 +2380,7 @@
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B14" t="s">
         <v>60</v>
@@ -2407,7 +2420,7 @@
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A16">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B16" t="s">
         <v>65</v>
@@ -2627,10 +2640,10 @@
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A27">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B27" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C27" t="s">
         <v>13</v>
@@ -2642,7 +2655,7 @@
         <v>6</v>
       </c>
       <c r="F27">
-        <v>2017</v>
+        <v>2023</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.35">
@@ -2650,7 +2663,7 @@
         <v>1</v>
       </c>
       <c r="B28" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C28" t="s">
         <v>13</v>
@@ -2662,15 +2675,15 @@
         <v>6</v>
       </c>
       <c r="F28">
-        <v>2023</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A29">
-        <v>1</v>
+      <c r="A29" t="s">
+        <v>26</v>
       </c>
       <c r="B29" t="s">
-        <v>72</v>
+        <v>352</v>
       </c>
       <c r="C29" t="s">
         <v>13</v>
@@ -2682,38 +2695,38 @@
         <v>6</v>
       </c>
       <c r="F29">
-        <v>2025</v>
+        <v>2019</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A30" t="s">
-        <v>26</v>
+      <c r="A30">
+        <v>2</v>
       </c>
       <c r="B30" t="s">
-        <v>352</v>
+        <v>32</v>
       </c>
       <c r="C30" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="D30" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E30" t="s">
         <v>6</v>
       </c>
       <c r="F30">
-        <v>2019</v>
+        <v>2013</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A31">
-        <v>2</v>
+      <c r="A31" t="s">
+        <v>26</v>
       </c>
       <c r="B31" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="C31" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="D31" t="s">
         <v>9</v>
@@ -2722,15 +2735,15 @@
         <v>6</v>
       </c>
       <c r="F31">
-        <v>2013</v>
+        <v>2022</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A32" t="s">
-        <v>26</v>
+      <c r="A32">
+        <v>2</v>
       </c>
       <c r="B32" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C32" t="s">
         <v>12</v>
@@ -2742,7 +2755,7 @@
         <v>6</v>
       </c>
       <c r="F32">
-        <v>2022</v>
+        <v>2024</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.35">
@@ -2750,7 +2763,7 @@
         <v>1</v>
       </c>
       <c r="B33" t="s">
-        <v>36</v>
+        <v>75</v>
       </c>
       <c r="C33" t="s">
         <v>12</v>
@@ -2770,10 +2783,10 @@
         <v>1</v>
       </c>
       <c r="B34" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="C34" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D34" t="s">
         <v>9</v>
@@ -2782,7 +2795,7 @@
         <v>6</v>
       </c>
       <c r="F34">
-        <v>2024</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.35">
@@ -2790,7 +2803,7 @@
         <v>2</v>
       </c>
       <c r="B35" t="s">
-        <v>77</v>
+        <v>39</v>
       </c>
       <c r="C35" t="s">
         <v>14</v>
@@ -2802,15 +2815,15 @@
         <v>6</v>
       </c>
       <c r="F35">
-        <v>2025</v>
+        <v>2026</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A36" t="s">
-        <v>53</v>
+      <c r="A36">
+        <v>1</v>
       </c>
       <c r="B36" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C36" t="s">
         <v>14</v>
@@ -2822,18 +2835,18 @@
         <v>6</v>
       </c>
       <c r="F36">
-        <v>2026</v>
+        <v>2022</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A37">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B37" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C37" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D37" t="s">
         <v>9</v>
@@ -2842,15 +2855,15 @@
         <v>6</v>
       </c>
       <c r="F37">
-        <v>2022</v>
+        <v>2024</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A38">
-        <v>2</v>
+      <c r="A38" t="s">
+        <v>26</v>
       </c>
       <c r="B38" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C38" t="s">
         <v>13</v>
@@ -2862,15 +2875,15 @@
         <v>6</v>
       </c>
       <c r="F38">
-        <v>2024</v>
+        <v>2022</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A39" t="s">
-        <v>26</v>
+      <c r="A39">
+        <v>1</v>
       </c>
       <c r="B39" t="s">
-        <v>37</v>
+        <v>76</v>
       </c>
       <c r="C39" t="s">
         <v>13</v>
@@ -2882,15 +2895,15 @@
         <v>6</v>
       </c>
       <c r="F39">
-        <v>2022</v>
+        <v>2024</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A40">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B40" t="s">
-        <v>76</v>
+        <v>358</v>
       </c>
       <c r="C40" t="s">
         <v>13</v>
@@ -2902,27 +2915,27 @@
         <v>6</v>
       </c>
       <c r="F40">
-        <v>2024</v>
+        <v>2026</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A41">
-        <v>1</v>
+      <c r="A41" t="s">
+        <v>26</v>
       </c>
       <c r="B41" t="s">
-        <v>358</v>
+        <v>78</v>
       </c>
       <c r="C41" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="D41" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="E41" t="s">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="F41">
-        <v>2026</v>
+        <v>2018</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.35">
@@ -2930,10 +2943,10 @@
         <v>26</v>
       </c>
       <c r="B42" t="s">
-        <v>78</v>
+        <v>46</v>
       </c>
       <c r="C42" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="D42" t="s">
         <v>21</v>
@@ -2942,15 +2955,15 @@
         <v>22</v>
       </c>
       <c r="F42">
-        <v>2018</v>
+        <v>2016</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A43" t="s">
-        <v>26</v>
+      <c r="A43">
+        <v>1</v>
       </c>
       <c r="B43" t="s">
-        <v>46</v>
+        <v>79</v>
       </c>
       <c r="C43" t="s">
         <v>12</v>
@@ -2962,18 +2975,18 @@
         <v>22</v>
       </c>
       <c r="F43">
-        <v>2016</v>
+        <v>2019</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A44">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B44" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="C44" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D44" t="s">
         <v>21</v>
@@ -2982,15 +2995,15 @@
         <v>22</v>
       </c>
       <c r="F44">
-        <v>2019</v>
+        <v>2018</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A45">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B45" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C45" t="s">
         <v>14</v>
@@ -3002,7 +3015,7 @@
         <v>22</v>
       </c>
       <c r="F45">
-        <v>2018</v>
+        <v>2026</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.35">
@@ -3010,10 +3023,10 @@
         <v>1</v>
       </c>
       <c r="B46" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="C46" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D46" t="s">
         <v>21</v>
@@ -3022,15 +3035,15 @@
         <v>22</v>
       </c>
       <c r="F46">
-        <v>2026</v>
+        <v>2021</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A47">
-        <v>1</v>
+      <c r="A47" t="s">
+        <v>26</v>
       </c>
       <c r="B47" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C47" t="s">
         <v>13</v>
@@ -3042,15 +3055,15 @@
         <v>22</v>
       </c>
       <c r="F47">
-        <v>2021</v>
+        <v>2023</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A48" t="s">
-        <v>26</v>
+      <c r="A48">
+        <v>1</v>
       </c>
       <c r="B48" t="s">
-        <v>81</v>
+        <v>363</v>
       </c>
       <c r="C48" t="s">
         <v>13</v>
@@ -3062,47 +3075,47 @@
         <v>22</v>
       </c>
       <c r="F48">
-        <v>2023</v>
+        <v>2026</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A49">
-        <v>1</v>
+      <c r="A49" t="s">
+        <v>26</v>
       </c>
       <c r="B49" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="C49" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="D49" t="s">
-        <v>21</v>
+        <v>87</v>
       </c>
       <c r="E49" t="s">
         <v>22</v>
       </c>
       <c r="F49">
-        <v>2026</v>
+        <v>2020</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A50">
-        <v>1</v>
+      <c r="A50" t="s">
+        <v>53</v>
       </c>
       <c r="B50" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="C50" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D50" t="s">
-        <v>21</v>
+        <v>87</v>
       </c>
       <c r="E50" t="s">
         <v>22</v>
       </c>
       <c r="F50">
-        <v>2024</v>
+        <v>2023</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.35">
@@ -3110,30 +3123,30 @@
         <v>1</v>
       </c>
       <c r="B51" t="s">
-        <v>363</v>
+        <v>89</v>
       </c>
       <c r="C51" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D51" t="s">
-        <v>21</v>
+        <v>87</v>
       </c>
       <c r="E51" t="s">
         <v>22</v>
       </c>
       <c r="F51">
-        <v>2026</v>
+        <v>2017</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A52" t="s">
-        <v>26</v>
+      <c r="A52">
+        <v>1</v>
       </c>
       <c r="B52" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="C52" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="D52" t="s">
         <v>87</v>
@@ -3142,18 +3155,18 @@
         <v>22</v>
       </c>
       <c r="F52">
-        <v>2020</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A53" t="s">
-        <v>53</v>
+      <c r="A53">
+        <v>2</v>
       </c>
       <c r="B53" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="C53" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D53" t="s">
         <v>87</v>
@@ -3162,18 +3175,18 @@
         <v>22</v>
       </c>
       <c r="F53">
-        <v>2023</v>
+        <v>2018</v>
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A54">
-        <v>1</v>
+      <c r="A54" t="s">
+        <v>26</v>
       </c>
       <c r="B54" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="C54" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D54" t="s">
         <v>87</v>
@@ -3182,18 +3195,18 @@
         <v>22</v>
       </c>
       <c r="F54">
-        <v>2017</v>
+        <v>2021</v>
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A55">
-        <v>1</v>
+      <c r="A55" t="s">
+        <v>26</v>
       </c>
       <c r="B55" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="C55" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D55" t="s">
         <v>87</v>
@@ -3202,18 +3215,18 @@
         <v>22</v>
       </c>
       <c r="F55">
-        <v>2025</v>
+        <v>2020</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A56">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B56" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="C56" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D56" t="s">
         <v>87</v>
@@ -3222,27 +3235,27 @@
         <v>22</v>
       </c>
       <c r="F56">
-        <v>2018</v>
+        <v>2023</v>
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A57" t="s">
-        <v>26</v>
+      <c r="A57">
+        <v>1</v>
       </c>
       <c r="B57" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="C57" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="D57" t="s">
-        <v>87</v>
+        <v>97</v>
       </c>
       <c r="E57" t="s">
         <v>22</v>
       </c>
       <c r="F57">
-        <v>2021</v>
+        <v>2017</v>
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.35">
@@ -3250,19 +3263,19 @@
         <v>53</v>
       </c>
       <c r="B58" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="C58" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D58" t="s">
-        <v>87</v>
+        <v>97</v>
       </c>
       <c r="E58" t="s">
         <v>22</v>
       </c>
       <c r="F58">
-        <v>2020</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.35">
@@ -3270,19 +3283,19 @@
         <v>1</v>
       </c>
       <c r="B59" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="C59" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D59" t="s">
-        <v>87</v>
+        <v>97</v>
       </c>
       <c r="E59" t="s">
         <v>22</v>
       </c>
       <c r="F59">
-        <v>2023</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.35">
@@ -3290,10 +3303,10 @@
         <v>1</v>
       </c>
       <c r="B60" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="C60" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="D60" t="s">
         <v>97</v>
@@ -3302,7 +3315,7 @@
         <v>22</v>
       </c>
       <c r="F60">
-        <v>2017</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.35">
@@ -3310,10 +3323,10 @@
         <v>53</v>
       </c>
       <c r="B61" t="s">
-        <v>98</v>
+        <v>105</v>
       </c>
       <c r="C61" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D61" t="s">
         <v>97</v>
@@ -3326,14 +3339,14 @@
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A62">
-        <v>1</v>
+      <c r="A62" t="s">
+        <v>53</v>
       </c>
       <c r="B62" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="C62" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D62" t="s">
         <v>97</v>
@@ -3342,18 +3355,18 @@
         <v>22</v>
       </c>
       <c r="F62">
-        <v>2025</v>
+        <v>2026</v>
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A63">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B63" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="C63" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D63" t="s">
         <v>97</v>
@@ -3362,18 +3375,18 @@
         <v>22</v>
       </c>
       <c r="F63">
-        <v>2025</v>
+        <v>2020</v>
       </c>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A64">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B64" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="C64" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D64" t="s">
         <v>97</v>
@@ -3382,15 +3395,15 @@
         <v>22</v>
       </c>
       <c r="F64">
-        <v>2025</v>
+        <v>2026</v>
       </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A65" t="s">
-        <v>53</v>
+      <c r="A65">
+        <v>1</v>
       </c>
       <c r="B65" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="C65" t="s">
         <v>13</v>
@@ -3402,7 +3415,7 @@
         <v>22</v>
       </c>
       <c r="F65">
-        <v>2026</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.35">
@@ -3410,59 +3423,59 @@
         <v>2</v>
       </c>
       <c r="B66" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="C66" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="D66" t="s">
-        <v>97</v>
+        <v>107</v>
       </c>
       <c r="E66" t="s">
         <v>22</v>
       </c>
       <c r="F66">
-        <v>2020</v>
+        <v>2005</v>
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A67">
-        <v>2</v>
+      <c r="A67" t="s">
+        <v>53</v>
       </c>
       <c r="B67" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="C67" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D67" t="s">
-        <v>97</v>
+        <v>107</v>
       </c>
       <c r="E67" t="s">
         <v>22</v>
       </c>
       <c r="F67">
-        <v>2026</v>
+        <v>2022</v>
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A68">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B68" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="C68" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D68" t="s">
-        <v>97</v>
+        <v>107</v>
       </c>
       <c r="E68" t="s">
         <v>22</v>
       </c>
       <c r="F68">
-        <v>2025</v>
+        <v>2020</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.35">
@@ -3470,10 +3483,10 @@
         <v>2</v>
       </c>
       <c r="B69" t="s">
-        <v>106</v>
+        <v>114</v>
       </c>
       <c r="C69" t="s">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="D69" t="s">
         <v>107</v>
@@ -3482,18 +3495,18 @@
         <v>22</v>
       </c>
       <c r="F69">
-        <v>2005</v>
+        <v>2021</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A70" t="s">
-        <v>53</v>
+      <c r="A70">
+        <v>1</v>
       </c>
       <c r="B70" t="s">
-        <v>108</v>
+        <v>115</v>
       </c>
       <c r="C70" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D70" t="s">
         <v>107</v>
@@ -3502,18 +3515,18 @@
         <v>22</v>
       </c>
       <c r="F70">
-        <v>2022</v>
+        <v>2023</v>
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A71">
-        <v>2</v>
+      <c r="A71" t="s">
+        <v>53</v>
       </c>
       <c r="B71" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C71" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D71" t="s">
         <v>107</v>
@@ -3522,18 +3535,18 @@
         <v>22</v>
       </c>
       <c r="F71">
-        <v>2020</v>
+        <v>2019</v>
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A72">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B72" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="C72" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D72" t="s">
         <v>107</v>
@@ -3542,7 +3555,7 @@
         <v>22</v>
       </c>
       <c r="F72">
-        <v>2021</v>
+        <v>2024</v>
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.35">
@@ -3550,10 +3563,10 @@
         <v>1</v>
       </c>
       <c r="B73" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="C73" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D73" t="s">
         <v>107</v>
@@ -3562,7 +3575,7 @@
         <v>22</v>
       </c>
       <c r="F73">
-        <v>2023</v>
+        <v>2026</v>
       </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.35">
@@ -3570,70 +3583,70 @@
         <v>53</v>
       </c>
       <c r="B74" t="s">
-        <v>110</v>
+        <v>116</v>
       </c>
       <c r="C74" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="D74" t="s">
-        <v>107</v>
+        <v>117</v>
       </c>
       <c r="E74" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="F74">
+        <v>2023</v>
+      </c>
+    </row>
+    <row r="75" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A75" t="s">
+        <v>53</v>
+      </c>
+      <c r="B75" t="s">
+        <v>118</v>
+      </c>
+      <c r="C75" t="s">
+        <v>12</v>
+      </c>
+      <c r="D75" t="s">
+        <v>117</v>
+      </c>
+      <c r="E75" t="s">
+        <v>16</v>
+      </c>
+      <c r="F75">
         <v>2019</v>
-      </c>
-    </row>
-    <row r="75" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A75">
-        <v>1</v>
-      </c>
-      <c r="B75" t="s">
-        <v>112</v>
-      </c>
-      <c r="C75" t="s">
-        <v>13</v>
-      </c>
-      <c r="D75" t="s">
-        <v>107</v>
-      </c>
-      <c r="E75" t="s">
-        <v>22</v>
-      </c>
-      <c r="F75">
-        <v>2024</v>
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A76">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B76" t="s">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="C76" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D76" t="s">
-        <v>107</v>
+        <v>117</v>
       </c>
       <c r="E76" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="F76">
-        <v>2026</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A77" t="s">
-        <v>53</v>
+      <c r="A77">
+        <v>3</v>
       </c>
       <c r="B77" t="s">
-        <v>116</v>
+        <v>126</v>
       </c>
       <c r="C77" t="s">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="D77" t="s">
         <v>117</v>
@@ -3642,18 +3655,18 @@
         <v>16</v>
       </c>
       <c r="F77">
-        <v>2023</v>
+        <v>2018</v>
       </c>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A78" t="s">
-        <v>53</v>
+      <c r="A78">
+        <v>1</v>
       </c>
       <c r="B78" t="s">
-        <v>118</v>
+        <v>389</v>
       </c>
       <c r="C78" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D78" t="s">
         <v>117</v>
@@ -3666,14 +3679,14 @@
       </c>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A79">
-        <v>2</v>
+      <c r="A79" t="s">
+        <v>26</v>
       </c>
       <c r="B79" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C79" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D79" t="s">
         <v>117</v>
@@ -3682,18 +3695,18 @@
         <v>16</v>
       </c>
       <c r="F79">
-        <v>2025</v>
+        <v>2021</v>
       </c>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A80">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B80" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="C80" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D80" t="s">
         <v>117</v>
@@ -3702,7 +3715,7 @@
         <v>16</v>
       </c>
       <c r="F80">
-        <v>2018</v>
+        <v>2023</v>
       </c>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.35">
@@ -3710,10 +3723,10 @@
         <v>1</v>
       </c>
       <c r="B81" t="s">
-        <v>389</v>
+        <v>122</v>
       </c>
       <c r="C81" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D81" t="s">
         <v>117</v>
@@ -3722,15 +3735,15 @@
         <v>16</v>
       </c>
       <c r="F81">
-        <v>2019</v>
+        <v>2023</v>
       </c>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A82" t="s">
-        <v>26</v>
+      <c r="A82">
+        <v>1</v>
       </c>
       <c r="B82" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="C82" t="s">
         <v>13</v>
@@ -3742,7 +3755,7 @@
         <v>16</v>
       </c>
       <c r="F82">
-        <v>2021</v>
+        <v>2023</v>
       </c>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.35">
@@ -3750,7 +3763,7 @@
         <v>2</v>
       </c>
       <c r="B83" t="s">
-        <v>121</v>
+        <v>309</v>
       </c>
       <c r="C83" t="s">
         <v>13</v>
@@ -3762,7 +3775,7 @@
         <v>16</v>
       </c>
       <c r="F83">
-        <v>2023</v>
+        <v>2024</v>
       </c>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.35">
@@ -3770,39 +3783,39 @@
         <v>1</v>
       </c>
       <c r="B84" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="C84" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="D84" t="s">
-        <v>117</v>
+        <v>128</v>
       </c>
       <c r="E84" t="s">
         <v>16</v>
       </c>
       <c r="F84">
-        <v>2023</v>
+        <v>2019</v>
       </c>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A85">
-        <v>2</v>
+      <c r="A85" t="s">
+        <v>26</v>
       </c>
       <c r="B85" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="C85" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D85" t="s">
-        <v>117</v>
+        <v>128</v>
       </c>
       <c r="E85" t="s">
         <v>16</v>
       </c>
       <c r="F85">
-        <v>2023</v>
+        <v>2020</v>
       </c>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.35">
@@ -3810,50 +3823,50 @@
         <v>1</v>
       </c>
       <c r="B86" t="s">
-        <v>125</v>
+        <v>393</v>
       </c>
       <c r="C86" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D86" t="s">
-        <v>117</v>
+        <v>128</v>
       </c>
       <c r="E86" t="s">
         <v>16</v>
       </c>
       <c r="F86">
-        <v>2025</v>
+        <v>2026</v>
       </c>
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A87">
-        <v>2</v>
+      <c r="A87" t="s">
+        <v>26</v>
       </c>
       <c r="B87" t="s">
-        <v>309</v>
+        <v>134</v>
       </c>
       <c r="C87" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D87" t="s">
-        <v>117</v>
+        <v>128</v>
       </c>
       <c r="E87" t="s">
         <v>16</v>
       </c>
       <c r="F87">
-        <v>2024</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A88">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B88" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="C88" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="D88" t="s">
         <v>128</v>
@@ -3862,18 +3875,18 @@
         <v>16</v>
       </c>
       <c r="F88">
-        <v>2019</v>
+        <v>2016</v>
       </c>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A89" t="s">
-        <v>26</v>
+      <c r="A89">
+        <v>2</v>
       </c>
       <c r="B89" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="C89" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D89" t="s">
         <v>128</v>
@@ -3882,18 +3895,18 @@
         <v>16</v>
       </c>
       <c r="F89">
-        <v>2020</v>
+        <v>2013</v>
       </c>
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A90" t="s">
-        <v>26</v>
+      <c r="A90">
+        <v>2</v>
       </c>
       <c r="B90" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="C90" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D90" t="s">
         <v>128</v>
@@ -3902,61 +3915,61 @@
         <v>16</v>
       </c>
       <c r="F90">
-        <v>2025</v>
+        <v>2023</v>
       </c>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A91">
-        <v>1</v>
+      <c r="A91" t="s">
+        <v>26</v>
       </c>
       <c r="B91" t="s">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="C91" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="D91" t="s">
-        <v>128</v>
+        <v>136</v>
       </c>
       <c r="E91" t="s">
         <v>16</v>
       </c>
       <c r="F91">
-        <v>2016</v>
+        <v>2021</v>
       </c>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A92">
-        <v>2</v>
+      <c r="A92" t="s">
+        <v>53</v>
       </c>
       <c r="B92" t="s">
-        <v>131</v>
+        <v>137</v>
       </c>
       <c r="C92" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D92" t="s">
-        <v>128</v>
+        <v>136</v>
       </c>
       <c r="E92" t="s">
         <v>16</v>
       </c>
       <c r="F92">
-        <v>2013</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A93">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B93" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="C93" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D93" t="s">
-        <v>128</v>
+        <v>136</v>
       </c>
       <c r="E93" t="s">
         <v>16</v>
@@ -3966,14 +3979,14 @@
       </c>
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A94" t="s">
-        <v>26</v>
+      <c r="A94">
+        <v>1</v>
       </c>
       <c r="B94" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="C94" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="D94" t="s">
         <v>136</v>
@@ -3982,7 +3995,7 @@
         <v>16</v>
       </c>
       <c r="F94">
-        <v>2021</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.35">
@@ -3990,10 +4003,10 @@
         <v>2</v>
       </c>
       <c r="B95" t="s">
-        <v>137</v>
+        <v>145</v>
       </c>
       <c r="C95" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D95" t="s">
         <v>136</v>
@@ -4002,7 +4015,7 @@
         <v>16</v>
       </c>
       <c r="F95">
-        <v>2025</v>
+        <v>2023</v>
       </c>
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.35">
@@ -4010,10 +4023,10 @@
         <v>1</v>
       </c>
       <c r="B96" t="s">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="C96" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D96" t="s">
         <v>136</v>
@@ -4022,7 +4035,7 @@
         <v>16</v>
       </c>
       <c r="F96">
-        <v>2023</v>
+        <v>2026</v>
       </c>
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.35">
@@ -4030,10 +4043,10 @@
         <v>1</v>
       </c>
       <c r="B97" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C97" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D97" t="s">
         <v>136</v>
@@ -4042,7 +4055,7 @@
         <v>16</v>
       </c>
       <c r="F97">
-        <v>2025</v>
+        <v>2024</v>
       </c>
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.35">
@@ -4050,10 +4063,10 @@
         <v>2</v>
       </c>
       <c r="B98" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="C98" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D98" t="s">
         <v>136</v>
@@ -4062,18 +4075,18 @@
         <v>16</v>
       </c>
       <c r="F98">
-        <v>2023</v>
+        <v>2019</v>
       </c>
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A99">
-        <v>1</v>
+      <c r="A99" t="s">
+        <v>53</v>
       </c>
       <c r="B99" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="C99" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D99" t="s">
         <v>136</v>
@@ -4082,7 +4095,7 @@
         <v>16</v>
       </c>
       <c r="F99">
-        <v>2026</v>
+        <v>2023</v>
       </c>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.35">
@@ -4090,7 +4103,7 @@
         <v>1</v>
       </c>
       <c r="B100" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="C100" t="s">
         <v>13</v>
@@ -4102,7 +4115,7 @@
         <v>16</v>
       </c>
       <c r="F100">
-        <v>2024</v>
+        <v>2026</v>
       </c>
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.35">
@@ -4110,7 +4123,7 @@
         <v>2</v>
       </c>
       <c r="B101" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="C101" t="s">
         <v>13</v>
@@ -4122,47 +4135,47 @@
         <v>16</v>
       </c>
       <c r="F101">
-        <v>2019</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A102" t="s">
-        <v>53</v>
+      <c r="A102">
+        <v>1</v>
       </c>
       <c r="B102" t="s">
-        <v>142</v>
+        <v>41</v>
       </c>
       <c r="C102" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="D102" t="s">
-        <v>136</v>
+        <v>15</v>
       </c>
       <c r="E102" t="s">
         <v>16</v>
       </c>
       <c r="F102">
-        <v>2023</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A103">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B103" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="C103" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D103" t="s">
-        <v>136</v>
+        <v>15</v>
       </c>
       <c r="E103" t="s">
         <v>16</v>
       </c>
       <c r="F103">
-        <v>2026</v>
+        <v>2019</v>
       </c>
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.35">
@@ -4170,19 +4183,19 @@
         <v>2</v>
       </c>
       <c r="B104" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="C104" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D104" t="s">
-        <v>136</v>
+        <v>15</v>
       </c>
       <c r="E104" t="s">
         <v>16</v>
       </c>
       <c r="F104">
-        <v>2025</v>
+        <v>2023</v>
       </c>
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.35">
@@ -4190,10 +4203,10 @@
         <v>1</v>
       </c>
       <c r="B105" t="s">
-        <v>41</v>
+        <v>149</v>
       </c>
       <c r="C105" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="D105" t="s">
         <v>15</v>
@@ -4202,18 +4215,18 @@
         <v>16</v>
       </c>
       <c r="F105">
-        <v>2025</v>
+        <v>2026</v>
       </c>
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A106">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B106" t="s">
-        <v>147</v>
+        <v>154</v>
       </c>
       <c r="C106" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D106" t="s">
         <v>15</v>
@@ -4222,18 +4235,18 @@
         <v>16</v>
       </c>
       <c r="F106">
-        <v>2019</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A107">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B107" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="C107" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D107" t="s">
         <v>15</v>
@@ -4242,18 +4255,18 @@
         <v>16</v>
       </c>
       <c r="F107">
-        <v>2023</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A108">
-        <v>1</v>
+      <c r="A108" t="s">
+        <v>53</v>
       </c>
       <c r="B108" t="s">
-        <v>149</v>
+        <v>47</v>
       </c>
       <c r="C108" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D108" t="s">
         <v>15</v>
@@ -4267,13 +4280,13 @@
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A109">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B109" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="C109" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D109" t="s">
         <v>15</v>
@@ -4282,7 +4295,7 @@
         <v>16</v>
       </c>
       <c r="F109">
-        <v>2025</v>
+        <v>2022</v>
       </c>
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.35">
@@ -4290,7 +4303,7 @@
         <v>1</v>
       </c>
       <c r="B110" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="C110" t="s">
         <v>13</v>
@@ -4302,15 +4315,15 @@
         <v>16</v>
       </c>
       <c r="F110">
-        <v>2025</v>
+        <v>2018</v>
       </c>
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A111" t="s">
-        <v>53</v>
+      <c r="A111">
+        <v>1</v>
       </c>
       <c r="B111" t="s">
-        <v>47</v>
+        <v>153</v>
       </c>
       <c r="C111" t="s">
         <v>13</v>
@@ -4322,7 +4335,7 @@
         <v>16</v>
       </c>
       <c r="F111">
-        <v>2026</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.35">
@@ -4330,70 +4343,70 @@
         <v>2</v>
       </c>
       <c r="B112" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="C112" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="D112" t="s">
-        <v>15</v>
+        <v>156</v>
       </c>
       <c r="E112" t="s">
-        <v>16</v>
+        <v>157</v>
       </c>
       <c r="F112">
-        <v>2022</v>
+        <v>2024</v>
       </c>
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A113">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B113" t="s">
-        <v>152</v>
+        <v>158</v>
       </c>
       <c r="C113" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D113" t="s">
-        <v>15</v>
+        <v>156</v>
       </c>
       <c r="E113" t="s">
-        <v>16</v>
+        <v>157</v>
       </c>
       <c r="F113">
-        <v>2018</v>
+        <v>2020</v>
       </c>
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A114">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B114" t="s">
-        <v>153</v>
+        <v>159</v>
       </c>
       <c r="C114" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D114" t="s">
-        <v>15</v>
+        <v>156</v>
       </c>
       <c r="E114" t="s">
-        <v>16</v>
+        <v>157</v>
       </c>
       <c r="F114">
         <v>2025</v>
       </c>
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A115" t="s">
-        <v>53</v>
+      <c r="A115">
+        <v>1</v>
       </c>
       <c r="B115" t="s">
-        <v>155</v>
+        <v>160</v>
       </c>
       <c r="C115" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="D115" t="s">
         <v>156</v>
@@ -4402,7 +4415,7 @@
         <v>157</v>
       </c>
       <c r="F115">
-        <v>2024</v>
+        <v>2026</v>
       </c>
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.35">
@@ -4410,10 +4423,10 @@
         <v>2</v>
       </c>
       <c r="B116" t="s">
-        <v>158</v>
+        <v>165</v>
       </c>
       <c r="C116" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D116" t="s">
         <v>156</v>
@@ -4422,18 +4435,18 @@
         <v>157</v>
       </c>
       <c r="F116">
-        <v>2020</v>
+        <v>2017</v>
       </c>
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A117">
-        <v>2</v>
+      <c r="A117" t="s">
+        <v>53</v>
       </c>
       <c r="B117" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="C117" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D117" t="s">
         <v>156</v>
@@ -4442,18 +4455,18 @@
         <v>157</v>
       </c>
       <c r="F117">
-        <v>2025</v>
+        <v>2018</v>
       </c>
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A118">
-        <v>1</v>
+      <c r="A118" t="s">
+        <v>53</v>
       </c>
       <c r="B118" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="C118" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D118" t="s">
         <v>156</v>
@@ -4462,18 +4475,18 @@
         <v>157</v>
       </c>
       <c r="F118">
-        <v>2026</v>
+        <v>2021</v>
       </c>
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A119">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B119" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="C119" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D119" t="s">
         <v>156</v>
@@ -4482,15 +4495,15 @@
         <v>157</v>
       </c>
       <c r="F119">
-        <v>2017</v>
+        <v>2024</v>
       </c>
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A120" t="s">
-        <v>53</v>
+      <c r="A120">
+        <v>1</v>
       </c>
       <c r="B120" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="C120" t="s">
         <v>13</v>
@@ -4502,47 +4515,47 @@
         <v>157</v>
       </c>
       <c r="F120">
-        <v>2018</v>
+        <v>2023</v>
       </c>
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A121" t="s">
-        <v>53</v>
+        <v>26</v>
       </c>
       <c r="B121" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="C121" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="D121" t="s">
-        <v>156</v>
+        <v>167</v>
       </c>
       <c r="E121" t="s">
         <v>157</v>
       </c>
       <c r="F121">
-        <v>2021</v>
+        <v>2017</v>
       </c>
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A122">
-        <v>1</v>
+      <c r="A122" t="s">
+        <v>26</v>
       </c>
       <c r="B122" t="s">
-        <v>163</v>
+        <v>168</v>
       </c>
       <c r="C122" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D122" t="s">
-        <v>156</v>
+        <v>167</v>
       </c>
       <c r="E122" t="s">
         <v>157</v>
       </c>
       <c r="F122">
-        <v>2024</v>
+        <v>2022</v>
       </c>
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.35">
@@ -4550,19 +4563,19 @@
         <v>1</v>
       </c>
       <c r="B123" t="s">
-        <v>164</v>
+        <v>169</v>
       </c>
       <c r="C123" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D123" t="s">
-        <v>156</v>
+        <v>167</v>
       </c>
       <c r="E123" t="s">
         <v>157</v>
       </c>
       <c r="F123">
-        <v>2023</v>
+        <v>2026</v>
       </c>
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.35">
@@ -4570,10 +4583,10 @@
         <v>26</v>
       </c>
       <c r="B124" t="s">
-        <v>166</v>
+        <v>173</v>
       </c>
       <c r="C124" t="s">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="D124" t="s">
         <v>167</v>
@@ -4582,18 +4595,18 @@
         <v>157</v>
       </c>
       <c r="F124">
-        <v>2017</v>
+        <v>2013</v>
       </c>
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A125" t="s">
-        <v>26</v>
+      <c r="A125">
+        <v>1</v>
       </c>
       <c r="B125" t="s">
-        <v>168</v>
+        <v>419</v>
       </c>
       <c r="C125" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D125" t="s">
         <v>167</v>
@@ -4602,18 +4615,18 @@
         <v>157</v>
       </c>
       <c r="F125">
-        <v>2022</v>
+        <v>2026</v>
       </c>
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A126">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B126" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="C126" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D126" t="s">
         <v>167</v>
@@ -4622,18 +4635,18 @@
         <v>157</v>
       </c>
       <c r="F126">
-        <v>2026</v>
+        <v>2024</v>
       </c>
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A127" t="s">
-        <v>26</v>
+        <v>53</v>
       </c>
       <c r="B127" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C127" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D127" t="s">
         <v>167</v>
@@ -4642,7 +4655,7 @@
         <v>157</v>
       </c>
       <c r="F127">
-        <v>2013</v>
+        <v>2023</v>
       </c>
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.35">
@@ -4650,7 +4663,7 @@
         <v>1</v>
       </c>
       <c r="B128" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="C128" t="s">
         <v>13</v>
@@ -4662,7 +4675,7 @@
         <v>157</v>
       </c>
       <c r="F128">
-        <v>2026</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.35">
@@ -4670,39 +4683,39 @@
         <v>2</v>
       </c>
       <c r="B129" t="s">
-        <v>171</v>
+        <v>184</v>
       </c>
       <c r="C129" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="D129" t="s">
-        <v>167</v>
+        <v>185</v>
       </c>
       <c r="E129" t="s">
         <v>157</v>
       </c>
       <c r="F129">
-        <v>2024</v>
+        <v>2020</v>
       </c>
     </row>
     <row r="130" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A130" t="s">
-        <v>53</v>
+      <c r="A130">
+        <v>2</v>
       </c>
       <c r="B130" t="s">
-        <v>172</v>
+        <v>186</v>
       </c>
       <c r="C130" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D130" t="s">
-        <v>167</v>
+        <v>185</v>
       </c>
       <c r="E130" t="s">
         <v>157</v>
       </c>
       <c r="F130">
-        <v>2023</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.35">
@@ -4710,30 +4723,30 @@
         <v>1</v>
       </c>
       <c r="B131" t="s">
-        <v>417</v>
+        <v>187</v>
       </c>
       <c r="C131" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D131" t="s">
-        <v>167</v>
+        <v>185</v>
       </c>
       <c r="E131" t="s">
         <v>157</v>
       </c>
       <c r="F131">
-        <v>2025</v>
+        <v>2023</v>
       </c>
     </row>
     <row r="132" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A132">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B132" t="s">
-        <v>184</v>
+        <v>432</v>
       </c>
       <c r="C132" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="D132" t="s">
         <v>185</v>
@@ -4742,18 +4755,18 @@
         <v>157</v>
       </c>
       <c r="F132">
-        <v>2020</v>
+        <v>2024</v>
       </c>
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A133">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B133" t="s">
-        <v>186</v>
+        <v>192</v>
       </c>
       <c r="C133" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D133" t="s">
         <v>185</v>
@@ -4762,7 +4775,7 @@
         <v>157</v>
       </c>
       <c r="F133">
-        <v>2025</v>
+        <v>2022</v>
       </c>
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.35">
@@ -4770,10 +4783,10 @@
         <v>1</v>
       </c>
       <c r="B134" t="s">
-        <v>187</v>
+        <v>193</v>
       </c>
       <c r="C134" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D134" t="s">
         <v>185</v>
@@ -4782,18 +4795,18 @@
         <v>157</v>
       </c>
       <c r="F134">
-        <v>2023</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="135" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A135">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B135" t="s">
-        <v>432</v>
+        <v>188</v>
       </c>
       <c r="C135" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D135" t="s">
         <v>185</v>
@@ -4802,18 +4815,18 @@
         <v>157</v>
       </c>
       <c r="F135">
-        <v>2024</v>
+        <v>2023</v>
       </c>
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A136">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B136" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="C136" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D136" t="s">
         <v>185</v>
@@ -4822,18 +4835,18 @@
         <v>157</v>
       </c>
       <c r="F136">
-        <v>2022</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="137" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A137">
-        <v>1</v>
+      <c r="A137" t="s">
+        <v>53</v>
       </c>
       <c r="B137" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="C137" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D137" t="s">
         <v>185</v>
@@ -4842,7 +4855,7 @@
         <v>157</v>
       </c>
       <c r="F137">
-        <v>2025</v>
+        <v>2024</v>
       </c>
     </row>
     <row r="138" spans="1:6" x14ac:dyDescent="0.35">
@@ -4850,33 +4863,33 @@
         <v>2</v>
       </c>
       <c r="B138" t="s">
-        <v>188</v>
+        <v>174</v>
       </c>
       <c r="C138" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="D138" t="s">
-        <v>185</v>
+        <v>175</v>
       </c>
       <c r="E138" t="s">
         <v>157</v>
       </c>
       <c r="F138">
-        <v>2023</v>
+        <v>2012</v>
       </c>
     </row>
     <row r="139" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A139">
-        <v>2</v>
+      <c r="A139" t="s">
+        <v>26</v>
       </c>
       <c r="B139" t="s">
-        <v>189</v>
+        <v>176</v>
       </c>
       <c r="C139" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D139" t="s">
-        <v>185</v>
+        <v>175</v>
       </c>
       <c r="E139" t="s">
         <v>157</v>
@@ -4886,34 +4899,34 @@
       </c>
     </row>
     <row r="140" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A140" t="s">
-        <v>53</v>
+      <c r="A140">
+        <v>1</v>
       </c>
       <c r="B140" t="s">
-        <v>190</v>
+        <v>177</v>
       </c>
       <c r="C140" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D140" t="s">
-        <v>185</v>
+        <v>175</v>
       </c>
       <c r="E140" t="s">
         <v>157</v>
       </c>
       <c r="F140">
-        <v>2024</v>
+        <v>2026</v>
       </c>
     </row>
     <row r="141" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A141">
-        <v>2</v>
+      <c r="A141" t="s">
+        <v>26</v>
       </c>
       <c r="B141" t="s">
-        <v>174</v>
+        <v>182</v>
       </c>
       <c r="C141" t="s">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="D141" t="s">
         <v>175</v>
@@ -4922,18 +4935,18 @@
         <v>157</v>
       </c>
       <c r="F141">
-        <v>2012</v>
+        <v>2024</v>
       </c>
     </row>
     <row r="142" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A142" t="s">
-        <v>26</v>
+      <c r="A142">
+        <v>2</v>
       </c>
       <c r="B142" t="s">
-        <v>176</v>
+        <v>183</v>
       </c>
       <c r="C142" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D142" t="s">
         <v>175</v>
@@ -4942,18 +4955,18 @@
         <v>157</v>
       </c>
       <c r="F142">
-        <v>2025</v>
+        <v>2023</v>
       </c>
     </row>
     <row r="143" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A143">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B143" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C143" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D143" t="s">
         <v>175</v>
@@ -4962,18 +4975,18 @@
         <v>157</v>
       </c>
       <c r="F143">
-        <v>2026</v>
+        <v>2022</v>
       </c>
     </row>
     <row r="144" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A144" t="s">
-        <v>26</v>
+      <c r="A144">
+        <v>1</v>
       </c>
       <c r="B144" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="C144" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D144" t="s">
         <v>175</v>
@@ -4982,7 +4995,7 @@
         <v>157</v>
       </c>
       <c r="F144">
-        <v>2024</v>
+        <v>2020</v>
       </c>
     </row>
     <row r="145" spans="1:6" x14ac:dyDescent="0.35">
@@ -4990,10 +5003,10 @@
         <v>2</v>
       </c>
       <c r="B145" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="C145" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D145" t="s">
         <v>175</v>
@@ -5010,7 +5023,7 @@
         <v>1</v>
       </c>
       <c r="B146" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="C146" t="s">
         <v>13</v>
@@ -5022,78 +5035,78 @@
         <v>157</v>
       </c>
       <c r="F146">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="147" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A147" t="s">
+        <v>53</v>
+      </c>
+      <c r="B147" t="s">
+        <v>194</v>
+      </c>
+      <c r="C147" t="s">
+        <v>7</v>
+      </c>
+      <c r="D147" t="s">
+        <v>195</v>
+      </c>
+      <c r="E147" t="s">
+        <v>196</v>
+      </c>
+      <c r="F147">
+        <v>2016</v>
+      </c>
+    </row>
+    <row r="148" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A148" t="s">
+        <v>53</v>
+      </c>
+      <c r="B148" t="s">
+        <v>197</v>
+      </c>
+      <c r="C148" t="s">
+        <v>12</v>
+      </c>
+      <c r="D148" t="s">
+        <v>195</v>
+      </c>
+      <c r="E148" t="s">
+        <v>196</v>
+      </c>
+      <c r="F148">
+        <v>2021</v>
+      </c>
+    </row>
+    <row r="149" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A149" t="s">
+        <v>53</v>
+      </c>
+      <c r="B149" t="s">
+        <v>202</v>
+      </c>
+      <c r="C149" t="s">
+        <v>14</v>
+      </c>
+      <c r="D149" t="s">
+        <v>195</v>
+      </c>
+      <c r="E149" t="s">
+        <v>196</v>
+      </c>
+      <c r="F149">
         <v>2022</v>
-      </c>
-    </row>
-    <row r="147" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A147">
-        <v>1</v>
-      </c>
-      <c r="B147" t="s">
-        <v>179</v>
-      </c>
-      <c r="C147" t="s">
-        <v>13</v>
-      </c>
-      <c r="D147" t="s">
-        <v>175</v>
-      </c>
-      <c r="E147" t="s">
-        <v>157</v>
-      </c>
-      <c r="F147">
-        <v>2020</v>
-      </c>
-    </row>
-    <row r="148" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A148">
-        <v>2</v>
-      </c>
-      <c r="B148" t="s">
-        <v>180</v>
-      </c>
-      <c r="C148" t="s">
-        <v>13</v>
-      </c>
-      <c r="D148" t="s">
-        <v>175</v>
-      </c>
-      <c r="E148" t="s">
-        <v>157</v>
-      </c>
-      <c r="F148">
-        <v>2023</v>
-      </c>
-    </row>
-    <row r="149" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A149">
-        <v>1</v>
-      </c>
-      <c r="B149" t="s">
-        <v>181</v>
-      </c>
-      <c r="C149" t="s">
-        <v>13</v>
-      </c>
-      <c r="D149" t="s">
-        <v>175</v>
-      </c>
-      <c r="E149" t="s">
-        <v>157</v>
-      </c>
-      <c r="F149">
-        <v>2025</v>
       </c>
     </row>
     <row r="150" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A150" t="s">
-        <v>53</v>
+        <v>26</v>
       </c>
       <c r="B150" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="C150" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="D150" t="s">
         <v>195</v>
@@ -5102,18 +5115,18 @@
         <v>196</v>
       </c>
       <c r="F150">
-        <v>2016</v>
+        <v>2022</v>
       </c>
     </row>
     <row r="151" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A151" t="s">
-        <v>53</v>
+        <v>26</v>
       </c>
       <c r="B151" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="C151" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D151" t="s">
         <v>195</v>
@@ -5122,18 +5135,18 @@
         <v>196</v>
       </c>
       <c r="F151">
-        <v>2021</v>
+        <v>2020</v>
       </c>
     </row>
     <row r="152" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A152" t="s">
-        <v>53</v>
+      <c r="A152">
+        <v>1</v>
       </c>
       <c r="B152" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="C152" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D152" t="s">
         <v>195</v>
@@ -5142,15 +5155,15 @@
         <v>196</v>
       </c>
       <c r="F152">
-        <v>2022</v>
+        <v>2024</v>
       </c>
     </row>
     <row r="153" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A153" t="s">
-        <v>26</v>
+      <c r="A153">
+        <v>1</v>
       </c>
       <c r="B153" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="C153" t="s">
         <v>13</v>
@@ -5162,47 +5175,47 @@
         <v>196</v>
       </c>
       <c r="F153">
-        <v>2022</v>
+        <v>2019</v>
       </c>
     </row>
     <row r="154" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A154" t="s">
-        <v>26</v>
+      <c r="A154">
+        <v>1</v>
       </c>
       <c r="B154" t="s">
-        <v>199</v>
+        <v>443</v>
       </c>
       <c r="C154" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="D154" t="s">
-        <v>195</v>
+        <v>204</v>
       </c>
       <c r="E154" t="s">
         <v>196</v>
       </c>
       <c r="F154">
-        <v>2020</v>
+        <v>2024</v>
       </c>
     </row>
     <row r="155" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A155">
-        <v>1</v>
+      <c r="A155" t="s">
+        <v>53</v>
       </c>
       <c r="B155" t="s">
-        <v>200</v>
+        <v>205</v>
       </c>
       <c r="C155" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D155" t="s">
-        <v>195</v>
+        <v>204</v>
       </c>
       <c r="E155" t="s">
         <v>196</v>
       </c>
       <c r="F155">
-        <v>2024</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="156" spans="1:6" x14ac:dyDescent="0.35">
@@ -5210,13 +5223,13 @@
         <v>1</v>
       </c>
       <c r="B156" t="s">
-        <v>201</v>
+        <v>208</v>
       </c>
       <c r="C156" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D156" t="s">
-        <v>195</v>
+        <v>204</v>
       </c>
       <c r="E156" t="s">
         <v>196</v>
@@ -5227,13 +5240,13 @@
     </row>
     <row r="157" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A157">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B157" t="s">
-        <v>443</v>
+        <v>212</v>
       </c>
       <c r="C157" t="s">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="D157" t="s">
         <v>204</v>
@@ -5242,18 +5255,18 @@
         <v>196</v>
       </c>
       <c r="F157">
-        <v>2024</v>
+        <v>2022</v>
       </c>
     </row>
     <row r="158" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A158">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B158" t="s">
-        <v>205</v>
+        <v>213</v>
       </c>
       <c r="C158" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D158" t="s">
         <v>204</v>
@@ -5262,18 +5275,18 @@
         <v>196</v>
       </c>
       <c r="F158">
-        <v>2025</v>
+        <v>2024</v>
       </c>
     </row>
     <row r="159" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A159">
-        <v>1</v>
+      <c r="A159" t="s">
+        <v>26</v>
       </c>
       <c r="B159" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="C159" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D159" t="s">
         <v>204</v>
@@ -5290,10 +5303,10 @@
         <v>1</v>
       </c>
       <c r="B160" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="C160" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D160" t="s">
         <v>204</v>
@@ -5302,18 +5315,18 @@
         <v>196</v>
       </c>
       <c r="F160">
-        <v>2019</v>
+        <v>2026</v>
       </c>
     </row>
     <row r="161" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A161">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B161" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="C161" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D161" t="s">
         <v>204</v>
@@ -5322,7 +5335,7 @@
         <v>196</v>
       </c>
       <c r="F161">
-        <v>2022</v>
+        <v>2020</v>
       </c>
     </row>
     <row r="162" spans="1:6" x14ac:dyDescent="0.35">
@@ -5330,19 +5343,19 @@
         <v>1</v>
       </c>
       <c r="B162" t="s">
-        <v>213</v>
+        <v>448</v>
       </c>
       <c r="C162" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="D162" t="s">
-        <v>204</v>
+        <v>215</v>
       </c>
       <c r="E162" t="s">
         <v>196</v>
       </c>
       <c r="F162">
-        <v>2024</v>
+        <v>2023</v>
       </c>
     </row>
     <row r="163" spans="1:6" x14ac:dyDescent="0.35">
@@ -5350,70 +5363,70 @@
         <v>26</v>
       </c>
       <c r="B163" t="s">
-        <v>209</v>
+        <v>216</v>
       </c>
       <c r="C163" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D163" t="s">
-        <v>204</v>
+        <v>215</v>
       </c>
       <c r="E163" t="s">
         <v>196</v>
       </c>
       <c r="F163">
-        <v>2024</v>
+        <v>2018</v>
       </c>
     </row>
     <row r="164" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A164">
-        <v>1</v>
+      <c r="A164" t="s">
+        <v>53</v>
       </c>
       <c r="B164" t="s">
-        <v>210</v>
+        <v>223</v>
       </c>
       <c r="C164" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D164" t="s">
-        <v>204</v>
+        <v>215</v>
       </c>
       <c r="E164" t="s">
         <v>196</v>
       </c>
       <c r="F164">
-        <v>2026</v>
+        <v>2018</v>
       </c>
     </row>
     <row r="165" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A165">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B165" t="s">
-        <v>211</v>
+        <v>218</v>
       </c>
       <c r="C165" t="s">
         <v>13</v>
       </c>
       <c r="D165" t="s">
-        <v>204</v>
+        <v>215</v>
       </c>
       <c r="E165" t="s">
         <v>196</v>
       </c>
       <c r="F165">
-        <v>2020</v>
+        <v>2023</v>
       </c>
     </row>
     <row r="166" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A166">
-        <v>1</v>
+      <c r="A166" t="s">
+        <v>26</v>
       </c>
       <c r="B166" t="s">
-        <v>448</v>
+        <v>219</v>
       </c>
       <c r="C166" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="D166" t="s">
         <v>215</v>
@@ -5422,18 +5435,18 @@
         <v>196</v>
       </c>
       <c r="F166">
-        <v>2023</v>
+        <v>2021</v>
       </c>
     </row>
     <row r="167" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A167" t="s">
-        <v>26</v>
+      <c r="A167">
+        <v>2</v>
       </c>
       <c r="B167" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="C167" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D167" t="s">
         <v>215</v>
@@ -5442,7 +5455,7 @@
         <v>196</v>
       </c>
       <c r="F167">
-        <v>2018</v>
+        <v>2026</v>
       </c>
     </row>
     <row r="168" spans="1:6" x14ac:dyDescent="0.35">
@@ -5450,10 +5463,10 @@
         <v>1</v>
       </c>
       <c r="B168" t="s">
-        <v>450</v>
+        <v>221</v>
       </c>
       <c r="C168" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D168" t="s">
         <v>215</v>
@@ -5462,18 +5475,18 @@
         <v>196</v>
       </c>
       <c r="F168">
-        <v>2022</v>
+        <v>2019</v>
       </c>
     </row>
     <row r="169" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A169" t="s">
-        <v>53</v>
+      <c r="A169">
+        <v>1</v>
       </c>
       <c r="B169" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="C169" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D169" t="s">
         <v>215</v>
@@ -5482,118 +5495,118 @@
         <v>196</v>
       </c>
       <c r="F169">
-        <v>2018</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="170" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A170">
-        <v>2</v>
+      <c r="A170" t="s">
+        <v>53</v>
       </c>
       <c r="B170" t="s">
-        <v>218</v>
+        <v>224</v>
       </c>
       <c r="C170" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="D170" t="s">
-        <v>215</v>
+        <v>225</v>
       </c>
       <c r="E170" t="s">
         <v>196</v>
       </c>
       <c r="F170">
-        <v>2023</v>
+        <v>2024</v>
       </c>
     </row>
     <row r="171" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A171" t="s">
-        <v>26</v>
+      <c r="A171">
+        <v>2</v>
       </c>
       <c r="B171" t="s">
-        <v>219</v>
+        <v>227</v>
       </c>
       <c r="C171" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D171" t="s">
-        <v>215</v>
+        <v>225</v>
       </c>
       <c r="E171" t="s">
         <v>196</v>
       </c>
       <c r="F171">
-        <v>2021</v>
+        <v>2022</v>
       </c>
     </row>
     <row r="172" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A172">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B172" t="s">
-        <v>220</v>
+        <v>228</v>
       </c>
       <c r="C172" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D172" t="s">
-        <v>215</v>
+        <v>225</v>
       </c>
       <c r="E172" t="s">
         <v>196</v>
       </c>
       <c r="F172">
-        <v>2026</v>
+        <v>2017</v>
       </c>
     </row>
     <row r="173" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A173">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B173" t="s">
-        <v>221</v>
+        <v>232</v>
       </c>
       <c r="C173" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D173" t="s">
-        <v>215</v>
+        <v>225</v>
       </c>
       <c r="E173" t="s">
         <v>196</v>
       </c>
       <c r="F173">
-        <v>2019</v>
+        <v>2022</v>
       </c>
     </row>
     <row r="174" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A174">
-        <v>1</v>
+      <c r="A174" t="s">
+        <v>53</v>
       </c>
       <c r="B174" t="s">
-        <v>222</v>
+        <v>230</v>
       </c>
       <c r="C174" t="s">
         <v>13</v>
       </c>
       <c r="D174" t="s">
-        <v>215</v>
+        <v>225</v>
       </c>
       <c r="E174" t="s">
         <v>196</v>
       </c>
       <c r="F174">
-        <v>2025</v>
+        <v>2015</v>
       </c>
     </row>
     <row r="175" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A175" t="s">
-        <v>53</v>
+      <c r="A175">
+        <v>1</v>
       </c>
       <c r="B175" t="s">
-        <v>224</v>
+        <v>231</v>
       </c>
       <c r="C175" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="D175" t="s">
         <v>225</v>
@@ -5602,18 +5615,18 @@
         <v>196</v>
       </c>
       <c r="F175">
-        <v>2024</v>
+        <v>2026</v>
       </c>
     </row>
     <row r="176" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A176">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B176" t="s">
-        <v>226</v>
+        <v>457</v>
       </c>
       <c r="C176" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D176" t="s">
         <v>225</v>
@@ -5622,18 +5635,18 @@
         <v>196</v>
       </c>
       <c r="F176">
-        <v>2025</v>
+        <v>2021</v>
       </c>
     </row>
     <row r="177" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A177">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B177" t="s">
-        <v>227</v>
+        <v>550</v>
       </c>
       <c r="C177" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D177" t="s">
         <v>225</v>
@@ -5646,114 +5659,114 @@
       </c>
     </row>
     <row r="178" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A178">
-        <v>1</v>
+      <c r="A178" t="s">
+        <v>26</v>
       </c>
       <c r="B178" t="s">
-        <v>228</v>
+        <v>233</v>
       </c>
       <c r="C178" t="s">
+        <v>7</v>
+      </c>
+      <c r="D178" t="s">
+        <v>17</v>
+      </c>
+      <c r="E178" t="s">
+        <v>18</v>
+      </c>
+      <c r="F178">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="179" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A179" t="s">
+        <v>53</v>
+      </c>
+      <c r="B179" t="s">
+        <v>234</v>
+      </c>
+      <c r="C179" t="s">
         <v>12</v>
       </c>
-      <c r="D178" t="s">
-        <v>225</v>
-      </c>
-      <c r="E178" t="s">
-        <v>196</v>
-      </c>
-      <c r="F178">
-        <v>2017</v>
-      </c>
-    </row>
-    <row r="179" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A179">
+      <c r="D179" t="s">
+        <v>17</v>
+      </c>
+      <c r="E179" t="s">
+        <v>18</v>
+      </c>
+      <c r="F179">
+        <v>2020</v>
+      </c>
+    </row>
+    <row r="180" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A180">
         <v>2</v>
       </c>
-      <c r="B179" t="s">
-        <v>232</v>
-      </c>
-      <c r="C179" t="s">
+      <c r="B180" t="s">
+        <v>45</v>
+      </c>
+      <c r="C180" t="s">
+        <v>12</v>
+      </c>
+      <c r="D180" t="s">
+        <v>17</v>
+      </c>
+      <c r="E180" t="s">
+        <v>18</v>
+      </c>
+      <c r="F180">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="181" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A181">
+        <v>1</v>
+      </c>
+      <c r="B181" t="s">
+        <v>235</v>
+      </c>
+      <c r="C181" t="s">
+        <v>12</v>
+      </c>
+      <c r="D181" t="s">
+        <v>17</v>
+      </c>
+      <c r="E181" t="s">
+        <v>18</v>
+      </c>
+      <c r="F181">
+        <v>2023</v>
+      </c>
+    </row>
+    <row r="182" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A182" t="s">
+        <v>53</v>
+      </c>
+      <c r="B182" t="s">
+        <v>42</v>
+      </c>
+      <c r="C182" t="s">
         <v>14</v>
       </c>
-      <c r="D179" t="s">
-        <v>225</v>
-      </c>
-      <c r="E179" t="s">
-        <v>196</v>
-      </c>
-      <c r="F179">
-        <v>2022</v>
-      </c>
-    </row>
-    <row r="180" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A180" t="s">
-        <v>53</v>
-      </c>
-      <c r="B180" t="s">
-        <v>229</v>
-      </c>
-      <c r="C180" t="s">
-        <v>13</v>
-      </c>
-      <c r="D180" t="s">
-        <v>225</v>
-      </c>
-      <c r="E180" t="s">
-        <v>196</v>
-      </c>
-      <c r="F180">
-        <v>2019</v>
-      </c>
-    </row>
-    <row r="181" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A181" t="s">
-        <v>53</v>
-      </c>
-      <c r="B181" t="s">
-        <v>230</v>
-      </c>
-      <c r="C181" t="s">
-        <v>13</v>
-      </c>
-      <c r="D181" t="s">
-        <v>225</v>
-      </c>
-      <c r="E181" t="s">
-        <v>196</v>
-      </c>
-      <c r="F181">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="182" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A182">
-        <v>1</v>
-      </c>
-      <c r="B182" t="s">
-        <v>231</v>
-      </c>
-      <c r="C182" t="s">
-        <v>13</v>
-      </c>
       <c r="D182" t="s">
-        <v>225</v>
+        <v>17</v>
       </c>
       <c r="E182" t="s">
-        <v>196</v>
+        <v>18</v>
       </c>
       <c r="F182">
-        <v>2026</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="183" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A183" t="s">
-        <v>26</v>
+        <v>53</v>
       </c>
       <c r="B183" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="C183" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="D183" t="s">
         <v>17</v>
@@ -5770,10 +5783,10 @@
         <v>53</v>
       </c>
       <c r="B184" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="C184" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D184" t="s">
         <v>17</v>
@@ -5782,18 +5795,18 @@
         <v>18</v>
       </c>
       <c r="F184">
-        <v>2020</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="185" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A185">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B185" t="s">
-        <v>45</v>
+        <v>238</v>
       </c>
       <c r="C185" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D185" t="s">
         <v>17</v>
@@ -5802,7 +5815,7 @@
         <v>18</v>
       </c>
       <c r="F185">
-        <v>2025</v>
+        <v>2016</v>
       </c>
     </row>
     <row r="186" spans="1:6" x14ac:dyDescent="0.35">
@@ -5810,10 +5823,10 @@
         <v>1</v>
       </c>
       <c r="B186" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="C186" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D186" t="s">
         <v>17</v>
@@ -5822,87 +5835,87 @@
         <v>18</v>
       </c>
       <c r="F186">
-        <v>2023</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="187" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A187" t="s">
-        <v>53</v>
+        <v>26</v>
       </c>
       <c r="B187" t="s">
-        <v>42</v>
+        <v>242</v>
       </c>
       <c r="C187" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="D187" t="s">
-        <v>17</v>
+        <v>243</v>
       </c>
       <c r="E187" t="s">
         <v>18</v>
       </c>
       <c r="F187">
-        <v>2025</v>
+        <v>2016</v>
       </c>
     </row>
     <row r="188" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A188" t="s">
-        <v>53</v>
+        <v>26</v>
       </c>
       <c r="B188" t="s">
-        <v>236</v>
+        <v>244</v>
       </c>
       <c r="C188" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D188" t="s">
-        <v>17</v>
+        <v>243</v>
       </c>
       <c r="E188" t="s">
         <v>18</v>
       </c>
       <c r="F188">
-        <v>2024</v>
+        <v>2023</v>
       </c>
     </row>
     <row r="189" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A189" t="s">
-        <v>53</v>
+      <c r="A189">
+        <v>1</v>
       </c>
       <c r="B189" t="s">
-        <v>237</v>
+        <v>466</v>
       </c>
       <c r="C189" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D189" t="s">
-        <v>17</v>
+        <v>243</v>
       </c>
       <c r="E189" t="s">
         <v>18</v>
       </c>
       <c r="F189">
-        <v>2025</v>
+        <v>2024</v>
       </c>
     </row>
     <row r="190" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A190">
-        <v>2</v>
+      <c r="A190" t="s">
+        <v>53</v>
       </c>
       <c r="B190" t="s">
-        <v>238</v>
+        <v>248</v>
       </c>
       <c r="C190" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D190" t="s">
-        <v>17</v>
+        <v>243</v>
       </c>
       <c r="E190" t="s">
         <v>18</v>
       </c>
       <c r="F190">
-        <v>2016</v>
+        <v>2023</v>
       </c>
     </row>
     <row r="191" spans="1:6" x14ac:dyDescent="0.35">
@@ -5910,13 +5923,13 @@
         <v>1</v>
       </c>
       <c r="B191" t="s">
-        <v>239</v>
+        <v>245</v>
       </c>
       <c r="C191" t="s">
         <v>13</v>
       </c>
       <c r="D191" t="s">
-        <v>17</v>
+        <v>243</v>
       </c>
       <c r="E191" t="s">
         <v>18</v>
@@ -5926,23 +5939,23 @@
       </c>
     </row>
     <row r="192" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A192">
-        <v>1</v>
+      <c r="A192" t="s">
+        <v>26</v>
       </c>
       <c r="B192" t="s">
-        <v>240</v>
+        <v>246</v>
       </c>
       <c r="C192" t="s">
         <v>13</v>
       </c>
       <c r="D192" t="s">
-        <v>17</v>
+        <v>243</v>
       </c>
       <c r="E192" t="s">
         <v>18</v>
       </c>
       <c r="F192">
-        <v>2026</v>
+        <v>2021</v>
       </c>
     </row>
     <row r="193" spans="1:6" x14ac:dyDescent="0.35">
@@ -5950,10 +5963,10 @@
         <v>53</v>
       </c>
       <c r="B193" t="s">
-        <v>242</v>
+        <v>247</v>
       </c>
       <c r="C193" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="D193" t="s">
         <v>243</v>
@@ -5962,47 +5975,47 @@
         <v>18</v>
       </c>
       <c r="F193">
-        <v>2016</v>
+        <v>2022</v>
       </c>
     </row>
     <row r="194" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A194" t="s">
-        <v>26</v>
+        <v>53</v>
       </c>
       <c r="B194" t="s">
-        <v>244</v>
+        <v>249</v>
       </c>
       <c r="C194" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="D194" t="s">
-        <v>243</v>
+        <v>250</v>
       </c>
       <c r="E194" t="s">
         <v>18</v>
       </c>
       <c r="F194">
-        <v>2023</v>
+        <v>2020</v>
       </c>
     </row>
     <row r="195" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A195" t="s">
-        <v>53</v>
+      <c r="A195">
+        <v>1</v>
       </c>
       <c r="B195" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="C195" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D195" t="s">
-        <v>243</v>
+        <v>250</v>
       </c>
       <c r="E195" t="s">
         <v>18</v>
       </c>
       <c r="F195">
-        <v>2023</v>
+        <v>2024</v>
       </c>
     </row>
     <row r="196" spans="1:6" x14ac:dyDescent="0.35">
@@ -6010,39 +6023,39 @@
         <v>1</v>
       </c>
       <c r="B196" t="s">
-        <v>245</v>
+        <v>545</v>
       </c>
       <c r="C196" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D196" t="s">
-        <v>243</v>
+        <v>250</v>
       </c>
       <c r="E196" t="s">
         <v>18</v>
       </c>
       <c r="F196">
-        <v>2025</v>
+        <v>2022</v>
       </c>
     </row>
     <row r="197" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A197" t="s">
-        <v>26</v>
+      <c r="A197">
+        <v>1</v>
       </c>
       <c r="B197" t="s">
-        <v>246</v>
+        <v>253</v>
       </c>
       <c r="C197" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D197" t="s">
-        <v>243</v>
+        <v>250</v>
       </c>
       <c r="E197" t="s">
         <v>18</v>
       </c>
       <c r="F197">
-        <v>2021</v>
+        <v>2023</v>
       </c>
     </row>
     <row r="198" spans="1:6" x14ac:dyDescent="0.35">
@@ -6050,30 +6063,30 @@
         <v>53</v>
       </c>
       <c r="B198" t="s">
-        <v>247</v>
+        <v>475</v>
       </c>
       <c r="C198" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D198" t="s">
-        <v>243</v>
+        <v>250</v>
       </c>
       <c r="E198" t="s">
         <v>18</v>
       </c>
       <c r="F198">
-        <v>2022</v>
+        <v>2019</v>
       </c>
     </row>
     <row r="199" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A199">
-        <v>2</v>
+      <c r="A199" t="s">
+        <v>53</v>
       </c>
       <c r="B199" t="s">
-        <v>249</v>
+        <v>257</v>
       </c>
       <c r="C199" t="s">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="D199" t="s">
         <v>250</v>
@@ -6082,7 +6095,7 @@
         <v>18</v>
       </c>
       <c r="F199">
-        <v>2020</v>
+        <v>2023</v>
       </c>
     </row>
     <row r="200" spans="1:6" x14ac:dyDescent="0.35">
@@ -6090,10 +6103,10 @@
         <v>1</v>
       </c>
       <c r="B200" t="s">
-        <v>251</v>
+        <v>258</v>
       </c>
       <c r="C200" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D200" t="s">
         <v>250</v>
@@ -6102,18 +6115,18 @@
         <v>18</v>
       </c>
       <c r="F200">
-        <v>2024</v>
+        <v>2017</v>
       </c>
     </row>
     <row r="201" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A201">
-        <v>1</v>
+      <c r="A201" t="s">
+        <v>26</v>
       </c>
       <c r="B201" t="s">
-        <v>545</v>
+        <v>254</v>
       </c>
       <c r="C201" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D201" t="s">
         <v>250</v>
@@ -6126,14 +6139,14 @@
       </c>
     </row>
     <row r="202" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A202">
-        <v>1</v>
+      <c r="A202" t="s">
+        <v>53</v>
       </c>
       <c r="B202" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="C202" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D202" t="s">
         <v>250</v>
@@ -6142,18 +6155,18 @@
         <v>18</v>
       </c>
       <c r="F202">
-        <v>2023</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="203" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A203" t="s">
-        <v>53</v>
+      <c r="A203">
+        <v>1</v>
       </c>
       <c r="B203" t="s">
-        <v>475</v>
+        <v>256</v>
       </c>
       <c r="C203" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D203" t="s">
         <v>250</v>
@@ -6162,18 +6175,18 @@
         <v>18</v>
       </c>
       <c r="F203">
-        <v>2019</v>
+        <v>2022</v>
       </c>
     </row>
     <row r="204" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A204" t="s">
-        <v>53</v>
+      <c r="A204">
+        <v>1</v>
       </c>
       <c r="B204" t="s">
-        <v>257</v>
+        <v>549</v>
       </c>
       <c r="C204" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D204" t="s">
         <v>250</v>
@@ -6182,18 +6195,18 @@
         <v>18</v>
       </c>
       <c r="F204">
-        <v>2023</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="205" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A205">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B205" t="s">
-        <v>258</v>
+        <v>478</v>
       </c>
       <c r="C205" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D205" t="s">
         <v>250</v>
@@ -6202,27 +6215,27 @@
         <v>18</v>
       </c>
       <c r="F205">
-        <v>2017</v>
+        <v>2023</v>
       </c>
     </row>
     <row r="206" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A206" t="s">
-        <v>53</v>
+      <c r="A206">
+        <v>2</v>
       </c>
       <c r="B206" t="s">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="C206" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="D206" t="s">
-        <v>250</v>
+        <v>260</v>
       </c>
       <c r="E206" t="s">
         <v>18</v>
       </c>
       <c r="F206">
-        <v>2022</v>
+        <v>2019</v>
       </c>
     </row>
     <row r="207" spans="1:6" x14ac:dyDescent="0.35">
@@ -6230,33 +6243,33 @@
         <v>53</v>
       </c>
       <c r="B207" t="s">
-        <v>255</v>
+        <v>261</v>
       </c>
       <c r="C207" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D207" t="s">
-        <v>250</v>
+        <v>260</v>
       </c>
       <c r="E207" t="s">
         <v>18</v>
       </c>
       <c r="F207">
-        <v>2025</v>
+        <v>2017</v>
       </c>
     </row>
     <row r="208" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A208">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B208" t="s">
-        <v>256</v>
+        <v>484</v>
       </c>
       <c r="C208" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D208" t="s">
-        <v>250</v>
+        <v>260</v>
       </c>
       <c r="E208" t="s">
         <v>18</v>
@@ -6270,30 +6283,30 @@
         <v>2</v>
       </c>
       <c r="B209" t="s">
-        <v>478</v>
+        <v>266</v>
       </c>
       <c r="C209" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D209" t="s">
-        <v>250</v>
+        <v>260</v>
       </c>
       <c r="E209" t="s">
         <v>18</v>
       </c>
       <c r="F209">
-        <v>2023</v>
+        <v>2019</v>
       </c>
     </row>
     <row r="210" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A210">
-        <v>2</v>
+      <c r="A210" t="s">
+        <v>26</v>
       </c>
       <c r="B210" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="C210" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="D210" t="s">
         <v>260</v>
@@ -6302,18 +6315,18 @@
         <v>18</v>
       </c>
       <c r="F210">
-        <v>2019</v>
+        <v>2020</v>
       </c>
     </row>
     <row r="211" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A211" t="s">
-        <v>53</v>
+      <c r="A211">
+        <v>2</v>
       </c>
       <c r="B211" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="C211" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D211" t="s">
         <v>260</v>
@@ -6322,18 +6335,18 @@
         <v>18</v>
       </c>
       <c r="F211">
-        <v>2017</v>
+        <v>2023</v>
       </c>
     </row>
     <row r="212" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A212">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B212" t="s">
-        <v>484</v>
+        <v>264</v>
       </c>
       <c r="C212" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D212" t="s">
         <v>260</v>
@@ -6342,18 +6355,18 @@
         <v>18</v>
       </c>
       <c r="F212">
-        <v>2022</v>
+        <v>2020</v>
       </c>
     </row>
     <row r="213" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A213">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B213" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="C213" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D213" t="s">
         <v>260</v>
@@ -6362,44 +6375,44 @@
         <v>18</v>
       </c>
       <c r="F213">
-        <v>2019</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="214" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A214" t="s">
+      <c r="A214">
+        <v>2</v>
+      </c>
+      <c r="B214" t="s">
+        <v>267</v>
+      </c>
+      <c r="C214" t="s">
+        <v>7</v>
+      </c>
+      <c r="D214" t="s">
+        <v>268</v>
+      </c>
+      <c r="E214" t="s">
+        <v>24</v>
+      </c>
+      <c r="F214">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="215" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A215" t="s">
         <v>26</v>
       </c>
-      <c r="B214" t="s">
-        <v>262</v>
-      </c>
-      <c r="C214" t="s">
-        <v>13</v>
-      </c>
-      <c r="D214" t="s">
-        <v>260</v>
-      </c>
-      <c r="E214" t="s">
-        <v>18</v>
-      </c>
-      <c r="F214">
-        <v>2020</v>
-      </c>
-    </row>
-    <row r="215" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A215">
-        <v>2</v>
-      </c>
       <c r="B215" t="s">
-        <v>263</v>
+        <v>269</v>
       </c>
       <c r="C215" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D215" t="s">
-        <v>260</v>
+        <v>268</v>
       </c>
       <c r="E215" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="F215">
         <v>2023</v>
@@ -6407,42 +6420,42 @@
     </row>
     <row r="216" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A216">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B216" t="s">
-        <v>264</v>
+        <v>270</v>
       </c>
       <c r="C216" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D216" t="s">
-        <v>260</v>
+        <v>268</v>
       </c>
       <c r="E216" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="F216">
-        <v>2020</v>
+        <v>2022</v>
       </c>
     </row>
     <row r="217" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A217">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B217" t="s">
-        <v>265</v>
+        <v>274</v>
       </c>
       <c r="C217" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D217" t="s">
-        <v>260</v>
+        <v>268</v>
       </c>
       <c r="E217" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="F217">
-        <v>2025</v>
+        <v>2021</v>
       </c>
     </row>
     <row r="218" spans="1:6" x14ac:dyDescent="0.35">
@@ -6450,10 +6463,10 @@
         <v>1</v>
       </c>
       <c r="B218" t="s">
-        <v>267</v>
+        <v>275</v>
       </c>
       <c r="C218" t="s">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="D218" t="s">
         <v>268</v>
@@ -6462,7 +6475,7 @@
         <v>24</v>
       </c>
       <c r="F218">
-        <v>2024</v>
+        <v>2016</v>
       </c>
     </row>
     <row r="219" spans="1:6" x14ac:dyDescent="0.35">
@@ -6470,10 +6483,10 @@
         <v>26</v>
       </c>
       <c r="B219" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="C219" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D219" t="s">
         <v>268</v>
@@ -6482,18 +6495,18 @@
         <v>24</v>
       </c>
       <c r="F219">
-        <v>2023</v>
+        <v>2022</v>
       </c>
     </row>
     <row r="220" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A220">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B220" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="C220" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D220" t="s">
         <v>268</v>
@@ -6507,13 +6520,13 @@
     </row>
     <row r="221" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A221">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B221" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="C221" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D221" t="s">
         <v>268</v>
@@ -6522,47 +6535,47 @@
         <v>24</v>
       </c>
       <c r="F221">
-        <v>2021</v>
+        <v>2026</v>
       </c>
     </row>
     <row r="222" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A222">
-        <v>1</v>
+      <c r="A222" t="s">
+        <v>26</v>
       </c>
       <c r="B222" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="C222" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="D222" t="s">
-        <v>268</v>
+        <v>277</v>
       </c>
       <c r="E222" t="s">
         <v>24</v>
       </c>
       <c r="F222">
-        <v>2016</v>
+        <v>2023</v>
       </c>
     </row>
     <row r="223" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A223" t="s">
-        <v>26</v>
+        <v>53</v>
       </c>
       <c r="B223" t="s">
-        <v>271</v>
+        <v>278</v>
       </c>
       <c r="C223" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D223" t="s">
-        <v>268</v>
+        <v>277</v>
       </c>
       <c r="E223" t="s">
         <v>24</v>
       </c>
       <c r="F223">
-        <v>2022</v>
+        <v>2021</v>
       </c>
     </row>
     <row r="224" spans="1:6" x14ac:dyDescent="0.35">
@@ -6570,50 +6583,50 @@
         <v>1</v>
       </c>
       <c r="B224" t="s">
-        <v>272</v>
+        <v>283</v>
       </c>
       <c r="C224" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D224" t="s">
-        <v>268</v>
+        <v>277</v>
       </c>
       <c r="E224" t="s">
         <v>24</v>
       </c>
       <c r="F224">
-        <v>2022</v>
+        <v>2021</v>
       </c>
     </row>
     <row r="225" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A225">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B225" t="s">
-        <v>273</v>
+        <v>284</v>
       </c>
       <c r="C225" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D225" t="s">
-        <v>268</v>
+        <v>277</v>
       </c>
       <c r="E225" t="s">
         <v>24</v>
       </c>
       <c r="F225">
-        <v>2026</v>
+        <v>2015</v>
       </c>
     </row>
     <row r="226" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A226" t="s">
-        <v>26</v>
+      <c r="A226">
+        <v>1</v>
       </c>
       <c r="B226" t="s">
-        <v>276</v>
+        <v>285</v>
       </c>
       <c r="C226" t="s">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="D226" t="s">
         <v>277</v>
@@ -6622,18 +6635,18 @@
         <v>24</v>
       </c>
       <c r="F226">
-        <v>2023</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="227" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A227" t="s">
-        <v>53</v>
+        <v>26</v>
       </c>
       <c r="B227" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="C227" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D227" t="s">
         <v>277</v>
@@ -6642,7 +6655,7 @@
         <v>24</v>
       </c>
       <c r="F227">
-        <v>2021</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="228" spans="1:6" x14ac:dyDescent="0.35">
@@ -6650,10 +6663,10 @@
         <v>1</v>
       </c>
       <c r="B228" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="C228" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D228" t="s">
         <v>277</v>
@@ -6662,18 +6675,18 @@
         <v>24</v>
       </c>
       <c r="F228">
-        <v>2021</v>
+        <v>2023</v>
       </c>
     </row>
     <row r="229" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A229">
-        <v>2</v>
+      <c r="A229" t="s">
+        <v>53</v>
       </c>
       <c r="B229" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="C229" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D229" t="s">
         <v>277</v>
@@ -6682,7 +6695,7 @@
         <v>24</v>
       </c>
       <c r="F229">
-        <v>2015</v>
+        <v>2024</v>
       </c>
     </row>
     <row r="230" spans="1:6" x14ac:dyDescent="0.35">
@@ -6690,10 +6703,10 @@
         <v>1</v>
       </c>
       <c r="B230" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="C230" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D230" t="s">
         <v>277</v>
@@ -6702,21 +6715,21 @@
         <v>24</v>
       </c>
       <c r="F230">
-        <v>2025</v>
+        <v>2022</v>
       </c>
     </row>
     <row r="231" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A231" t="s">
-        <v>26</v>
+        <v>53</v>
       </c>
       <c r="B231" t="s">
-        <v>279</v>
+        <v>286</v>
       </c>
       <c r="C231" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="D231" t="s">
-        <v>277</v>
+        <v>23</v>
       </c>
       <c r="E231" t="s">
         <v>24</v>
@@ -6727,42 +6740,42 @@
     </row>
     <row r="232" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A232">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B232" t="s">
-        <v>280</v>
+        <v>287</v>
       </c>
       <c r="C232" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D232" t="s">
-        <v>277</v>
+        <v>23</v>
       </c>
       <c r="E232" t="s">
         <v>24</v>
       </c>
       <c r="F232">
-        <v>2023</v>
+        <v>2017</v>
       </c>
     </row>
     <row r="233" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A233" t="s">
-        <v>53</v>
+      <c r="A233">
+        <v>1</v>
       </c>
       <c r="B233" t="s">
-        <v>281</v>
+        <v>288</v>
       </c>
       <c r="C233" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D233" t="s">
-        <v>277</v>
+        <v>23</v>
       </c>
       <c r="E233" t="s">
         <v>24</v>
       </c>
       <c r="F233">
-        <v>2024</v>
+        <v>2023</v>
       </c>
     </row>
     <row r="234" spans="1:6" x14ac:dyDescent="0.35">
@@ -6770,30 +6783,30 @@
         <v>1</v>
       </c>
       <c r="B234" t="s">
-        <v>282</v>
+        <v>289</v>
       </c>
       <c r="C234" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D234" t="s">
-        <v>277</v>
+        <v>23</v>
       </c>
       <c r="E234" t="s">
         <v>24</v>
       </c>
       <c r="F234">
-        <v>2022</v>
+        <v>2026</v>
       </c>
     </row>
     <row r="235" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A235" t="s">
-        <v>53</v>
+      <c r="A235">
+        <v>2</v>
       </c>
       <c r="B235" t="s">
-        <v>286</v>
+        <v>293</v>
       </c>
       <c r="C235" t="s">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="D235" t="s">
         <v>23</v>
@@ -6802,18 +6815,18 @@
         <v>24</v>
       </c>
       <c r="F235">
-        <v>2025</v>
+        <v>2020</v>
       </c>
     </row>
     <row r="236" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A236">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B236" t="s">
-        <v>287</v>
+        <v>294</v>
       </c>
       <c r="C236" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D236" t="s">
         <v>23</v>
@@ -6822,18 +6835,18 @@
         <v>24</v>
       </c>
       <c r="F236">
-        <v>2017</v>
+        <v>2019</v>
       </c>
     </row>
     <row r="237" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A237">
-        <v>1</v>
+      <c r="A237" t="s">
+        <v>26</v>
       </c>
       <c r="B237" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="C237" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D237" t="s">
         <v>23</v>
@@ -6842,7 +6855,7 @@
         <v>24</v>
       </c>
       <c r="F237">
-        <v>2023</v>
+        <v>2022</v>
       </c>
     </row>
     <row r="238" spans="1:6" x14ac:dyDescent="0.35">
@@ -6850,10 +6863,10 @@
         <v>1</v>
       </c>
       <c r="B238" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="C238" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D238" t="s">
         <v>23</v>
@@ -6866,14 +6879,14 @@
       </c>
     </row>
     <row r="239" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A239" t="s">
-        <v>53</v>
+      <c r="A239">
+        <v>2</v>
       </c>
       <c r="B239" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C239" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D239" t="s">
         <v>23</v>
@@ -6882,27 +6895,27 @@
         <v>24</v>
       </c>
       <c r="F239">
-        <v>2020</v>
+        <v>2024</v>
       </c>
     </row>
     <row r="240" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A240">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B240" t="s">
-        <v>294</v>
+        <v>509</v>
       </c>
       <c r="C240" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="D240" t="s">
-        <v>23</v>
+        <v>296</v>
       </c>
       <c r="E240" t="s">
         <v>24</v>
       </c>
       <c r="F240">
-        <v>2019</v>
+        <v>2018</v>
       </c>
     </row>
     <row r="241" spans="1:6" x14ac:dyDescent="0.35">
@@ -6910,19 +6923,19 @@
         <v>26</v>
       </c>
       <c r="B241" t="s">
-        <v>290</v>
+        <v>297</v>
       </c>
       <c r="C241" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D241" t="s">
-        <v>23</v>
+        <v>296</v>
       </c>
       <c r="E241" t="s">
         <v>24</v>
       </c>
       <c r="F241">
-        <v>2022</v>
+        <v>2024</v>
       </c>
     </row>
     <row r="242" spans="1:6" x14ac:dyDescent="0.35">
@@ -6930,50 +6943,50 @@
         <v>1</v>
       </c>
       <c r="B242" t="s">
-        <v>291</v>
+        <v>298</v>
       </c>
       <c r="C242" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D242" t="s">
-        <v>23</v>
+        <v>296</v>
       </c>
       <c r="E242" t="s">
         <v>24</v>
       </c>
       <c r="F242">
-        <v>2026</v>
+        <v>2021</v>
       </c>
     </row>
     <row r="243" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A243">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B243" t="s">
-        <v>292</v>
+        <v>299</v>
       </c>
       <c r="C243" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D243" t="s">
-        <v>23</v>
+        <v>296</v>
       </c>
       <c r="E243" t="s">
         <v>24</v>
       </c>
       <c r="F243">
-        <v>2024</v>
+        <v>2023</v>
       </c>
     </row>
     <row r="244" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A244" t="s">
-        <v>53</v>
+      <c r="A244">
+        <v>2</v>
       </c>
       <c r="B244" t="s">
-        <v>509</v>
+        <v>304</v>
       </c>
       <c r="C244" t="s">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="D244" t="s">
         <v>296</v>
@@ -6982,18 +6995,18 @@
         <v>24</v>
       </c>
       <c r="F244">
-        <v>2018</v>
+        <v>2022</v>
       </c>
     </row>
     <row r="245" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A245" t="s">
-        <v>53</v>
+      <c r="A245">
+        <v>1</v>
       </c>
       <c r="B245" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="C245" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D245" t="s">
         <v>296</v>
@@ -7002,18 +7015,18 @@
         <v>24</v>
       </c>
       <c r="F245">
-        <v>2024</v>
+        <v>2026</v>
       </c>
     </row>
     <row r="246" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A246">
-        <v>1</v>
+      <c r="A246" t="s">
+        <v>53</v>
       </c>
       <c r="B246" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="C246" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D246" t="s">
         <v>296</v>
@@ -7022,18 +7035,18 @@
         <v>24</v>
       </c>
       <c r="F246">
-        <v>2021</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="247" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A247">
-        <v>1</v>
+      <c r="A247" t="s">
+        <v>53</v>
       </c>
       <c r="B247" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="C247" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D247" t="s">
         <v>296</v>
@@ -7042,18 +7055,18 @@
         <v>24</v>
       </c>
       <c r="F247">
-        <v>2023</v>
+        <v>2017</v>
       </c>
     </row>
     <row r="248" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A248">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B248" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="C248" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D248" t="s">
         <v>296</v>
@@ -7062,7 +7075,7 @@
         <v>24</v>
       </c>
       <c r="F248">
-        <v>2022</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="249" spans="1:6" x14ac:dyDescent="0.35">
@@ -7070,19 +7083,19 @@
         <v>1</v>
       </c>
       <c r="B249" t="s">
-        <v>300</v>
+        <v>305</v>
       </c>
       <c r="C249" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="D249" t="s">
-        <v>296</v>
+        <v>306</v>
       </c>
       <c r="E249" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="F249">
-        <v>2026</v>
+        <v>2016</v>
       </c>
     </row>
     <row r="250" spans="1:6" x14ac:dyDescent="0.35">
@@ -7090,39 +7103,39 @@
         <v>53</v>
       </c>
       <c r="B250" t="s">
-        <v>301</v>
+        <v>307</v>
       </c>
       <c r="C250" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D250" t="s">
-        <v>296</v>
+        <v>306</v>
       </c>
       <c r="E250" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="F250">
-        <v>2025</v>
+        <v>2026</v>
       </c>
     </row>
     <row r="251" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A251" t="s">
-        <v>53</v>
+      <c r="A251">
+        <v>2</v>
       </c>
       <c r="B251" t="s">
-        <v>302</v>
+        <v>308</v>
       </c>
       <c r="C251" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D251" t="s">
-        <v>296</v>
+        <v>306</v>
       </c>
       <c r="E251" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="F251">
-        <v>2017</v>
+        <v>2022</v>
       </c>
     </row>
     <row r="252" spans="1:6" x14ac:dyDescent="0.35">
@@ -7130,30 +7143,30 @@
         <v>1</v>
       </c>
       <c r="B252" t="s">
-        <v>303</v>
+        <v>517</v>
       </c>
       <c r="C252" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D252" t="s">
-        <v>296</v>
+        <v>306</v>
       </c>
       <c r="E252" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="F252">
-        <v>2025</v>
+        <v>2022</v>
       </c>
     </row>
     <row r="253" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A253">
-        <v>1</v>
+      <c r="A253" t="s">
+        <v>26</v>
       </c>
       <c r="B253" t="s">
-        <v>305</v>
+        <v>312</v>
       </c>
       <c r="C253" t="s">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="D253" t="s">
         <v>306</v>
@@ -7162,18 +7175,18 @@
         <v>19</v>
       </c>
       <c r="F253">
-        <v>2016</v>
+        <v>2022</v>
       </c>
     </row>
     <row r="254" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A254" t="s">
-        <v>53</v>
+      <c r="A254">
+        <v>1</v>
       </c>
       <c r="B254" t="s">
-        <v>307</v>
+        <v>313</v>
       </c>
       <c r="C254" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D254" t="s">
         <v>306</v>
@@ -7182,18 +7195,18 @@
         <v>19</v>
       </c>
       <c r="F254">
-        <v>2026</v>
+        <v>2023</v>
       </c>
     </row>
     <row r="255" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A255">
-        <v>2</v>
+      <c r="A255" t="s">
+        <v>53</v>
       </c>
       <c r="B255" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="C255" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D255" t="s">
         <v>306</v>
@@ -7202,7 +7215,7 @@
         <v>19</v>
       </c>
       <c r="F255">
-        <v>2022</v>
+        <v>2023</v>
       </c>
     </row>
     <row r="256" spans="1:6" x14ac:dyDescent="0.35">
@@ -7210,10 +7223,10 @@
         <v>1</v>
       </c>
       <c r="B256" t="s">
-        <v>517</v>
+        <v>311</v>
       </c>
       <c r="C256" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D256" t="s">
         <v>306</v>
@@ -7222,7 +7235,7 @@
         <v>19</v>
       </c>
       <c r="F256">
-        <v>2022</v>
+        <v>2017</v>
       </c>
     </row>
     <row r="257" spans="1:6" x14ac:dyDescent="0.35">
@@ -7230,90 +7243,90 @@
         <v>26</v>
       </c>
       <c r="B257" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="C257" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="D257" t="s">
-        <v>306</v>
+        <v>20</v>
       </c>
       <c r="E257" t="s">
         <v>19</v>
       </c>
       <c r="F257">
-        <v>2022</v>
+        <v>2009</v>
       </c>
     </row>
     <row r="258" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A258">
-        <v>1</v>
+      <c r="A258" t="s">
+        <v>26</v>
       </c>
       <c r="B258" t="s">
-        <v>313</v>
+        <v>44</v>
       </c>
       <c r="C258" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D258" t="s">
-        <v>306</v>
+        <v>20</v>
       </c>
       <c r="E258" t="s">
         <v>19</v>
       </c>
       <c r="F258">
-        <v>2023</v>
+        <v>2022</v>
       </c>
     </row>
     <row r="259" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A259" t="s">
-        <v>53</v>
+      <c r="A259">
+        <v>2</v>
       </c>
       <c r="B259" t="s">
-        <v>310</v>
+        <v>315</v>
       </c>
       <c r="C259" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D259" t="s">
-        <v>306</v>
+        <v>20</v>
       </c>
       <c r="E259" t="s">
         <v>19</v>
       </c>
       <c r="F259">
-        <v>2023</v>
+        <v>2024</v>
       </c>
     </row>
     <row r="260" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A260">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B260" t="s">
-        <v>311</v>
+        <v>319</v>
       </c>
       <c r="C260" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D260" t="s">
-        <v>306</v>
+        <v>20</v>
       </c>
       <c r="E260" t="s">
         <v>19</v>
       </c>
       <c r="F260">
-        <v>2017</v>
+        <v>2020</v>
       </c>
     </row>
     <row r="261" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A261" t="s">
-        <v>26</v>
+      <c r="A261">
+        <v>2</v>
       </c>
       <c r="B261" t="s">
-        <v>314</v>
+        <v>320</v>
       </c>
       <c r="C261" t="s">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="D261" t="s">
         <v>20</v>
@@ -7322,7 +7335,7 @@
         <v>19</v>
       </c>
       <c r="F261">
-        <v>2009</v>
+        <v>2016</v>
       </c>
     </row>
     <row r="262" spans="1:6" x14ac:dyDescent="0.35">
@@ -7330,10 +7343,10 @@
         <v>26</v>
       </c>
       <c r="B262" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C262" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D262" t="s">
         <v>20</v>
@@ -7342,18 +7355,18 @@
         <v>19</v>
       </c>
       <c r="F262">
-        <v>2022</v>
+        <v>2023</v>
       </c>
     </row>
     <row r="263" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A263">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B263" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="C263" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D263" t="s">
         <v>20</v>
@@ -7362,18 +7375,18 @@
         <v>19</v>
       </c>
       <c r="F263">
-        <v>2024</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="264" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A264">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B264" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="C264" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D264" t="s">
         <v>20</v>
@@ -7382,41 +7395,41 @@
         <v>19</v>
       </c>
       <c r="F264">
-        <v>2020</v>
+        <v>2021</v>
       </c>
     </row>
     <row r="265" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A265">
-        <v>2</v>
+      <c r="A265" t="s">
+        <v>53</v>
       </c>
       <c r="B265" t="s">
-        <v>320</v>
+        <v>328</v>
       </c>
       <c r="C265" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="D265" t="s">
-        <v>20</v>
+        <v>329</v>
       </c>
       <c r="E265" t="s">
         <v>19</v>
       </c>
       <c r="F265">
-        <v>2016</v>
+        <v>2018</v>
       </c>
     </row>
     <row r="266" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A266" t="s">
-        <v>26</v>
+      <c r="A266">
+        <v>2</v>
       </c>
       <c r="B266" t="s">
-        <v>43</v>
+        <v>330</v>
       </c>
       <c r="C266" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D266" t="s">
-        <v>20</v>
+        <v>329</v>
       </c>
       <c r="E266" t="s">
         <v>19</v>
@@ -7430,50 +7443,50 @@
         <v>1</v>
       </c>
       <c r="B267" t="s">
-        <v>317</v>
+        <v>331</v>
       </c>
       <c r="C267" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D267" t="s">
-        <v>20</v>
+        <v>329</v>
       </c>
       <c r="E267" t="s">
         <v>19</v>
       </c>
       <c r="F267">
-        <v>2025</v>
+        <v>2024</v>
       </c>
     </row>
     <row r="268" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A268">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B268" t="s">
-        <v>318</v>
+        <v>332</v>
       </c>
       <c r="C268" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D268" t="s">
-        <v>20</v>
+        <v>329</v>
       </c>
       <c r="E268" t="s">
         <v>19</v>
       </c>
       <c r="F268">
-        <v>2021</v>
+        <v>2023</v>
       </c>
     </row>
     <row r="269" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A269" t="s">
-        <v>53</v>
+      <c r="A269">
+        <v>2</v>
       </c>
       <c r="B269" t="s">
-        <v>328</v>
+        <v>539</v>
       </c>
       <c r="C269" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="D269" t="s">
         <v>329</v>
@@ -7482,18 +7495,18 @@
         <v>19</v>
       </c>
       <c r="F269">
-        <v>2018</v>
+        <v>2026</v>
       </c>
     </row>
     <row r="270" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A270">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B270" t="s">
-        <v>330</v>
+        <v>337</v>
       </c>
       <c r="C270" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D270" t="s">
         <v>329</v>
@@ -7502,18 +7515,18 @@
         <v>19</v>
       </c>
       <c r="F270">
-        <v>2023</v>
+        <v>2024</v>
       </c>
     </row>
     <row r="271" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A271">
-        <v>1</v>
+      <c r="A271" t="s">
+        <v>26</v>
       </c>
       <c r="B271" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="C271" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D271" t="s">
         <v>329</v>
@@ -7522,7 +7535,7 @@
         <v>19</v>
       </c>
       <c r="F271">
-        <v>2024</v>
+        <v>2023</v>
       </c>
     </row>
     <row r="272" spans="1:6" x14ac:dyDescent="0.35">
@@ -7530,10 +7543,10 @@
         <v>2</v>
       </c>
       <c r="B272" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="C272" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D272" t="s">
         <v>329</v>
@@ -7542,7 +7555,7 @@
         <v>19</v>
       </c>
       <c r="F272">
-        <v>2023</v>
+        <v>2022</v>
       </c>
     </row>
     <row r="273" spans="1:6" x14ac:dyDescent="0.35">
@@ -7550,10 +7563,10 @@
         <v>2</v>
       </c>
       <c r="B273" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="C273" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D273" t="s">
         <v>329</v>
@@ -7562,15 +7575,15 @@
         <v>19</v>
       </c>
       <c r="F273">
-        <v>2024</v>
+        <v>2017</v>
       </c>
     </row>
     <row r="274" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A274" t="s">
-        <v>26</v>
+      <c r="A274">
+        <v>1</v>
       </c>
       <c r="B274" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="C274" t="s">
         <v>13</v>
@@ -7582,21 +7595,21 @@
         <v>19</v>
       </c>
       <c r="F274">
-        <v>2023</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="275" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A275">
-        <v>2</v>
+      <c r="A275" t="s">
+        <v>26</v>
       </c>
       <c r="B275" t="s">
-        <v>334</v>
+        <v>321</v>
       </c>
       <c r="C275" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="D275" t="s">
-        <v>329</v>
+        <v>322</v>
       </c>
       <c r="E275" t="s">
         <v>19</v>
@@ -7606,17 +7619,17 @@
       </c>
     </row>
     <row r="276" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A276">
-        <v>2</v>
+      <c r="A276" t="s">
+        <v>26</v>
       </c>
       <c r="B276" t="s">
-        <v>335</v>
+        <v>323</v>
       </c>
       <c r="C276" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D276" t="s">
-        <v>329</v>
+        <v>322</v>
       </c>
       <c r="E276" t="s">
         <v>19</v>
@@ -7630,30 +7643,30 @@
         <v>1</v>
       </c>
       <c r="B277" t="s">
-        <v>336</v>
+        <v>324</v>
       </c>
       <c r="C277" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D277" t="s">
-        <v>329</v>
+        <v>322</v>
       </c>
       <c r="E277" t="s">
         <v>19</v>
       </c>
       <c r="F277">
-        <v>2025</v>
+        <v>2026</v>
       </c>
     </row>
     <row r="278" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A278" t="s">
-        <v>26</v>
+      <c r="A278">
+        <v>2</v>
       </c>
       <c r="B278" t="s">
-        <v>321</v>
+        <v>548</v>
       </c>
       <c r="C278" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="D278" t="s">
         <v>322</v>
@@ -7662,7 +7675,7 @@
         <v>19</v>
       </c>
       <c r="F278">
-        <v>2022</v>
+        <v>2013</v>
       </c>
     </row>
     <row r="279" spans="1:6" x14ac:dyDescent="0.35">
@@ -7670,10 +7683,10 @@
         <v>26</v>
       </c>
       <c r="B279" t="s">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="C279" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D279" t="s">
         <v>322</v>
@@ -7686,14 +7699,14 @@
       </c>
     </row>
     <row r="280" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A280">
-        <v>1</v>
+      <c r="A280" t="s">
+        <v>26</v>
       </c>
       <c r="B280" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="C280" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D280" t="s">
         <v>322</v>
@@ -7702,18 +7715,18 @@
         <v>19</v>
       </c>
       <c r="F280">
-        <v>2026</v>
+        <v>2014</v>
       </c>
     </row>
     <row r="281" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A281" t="s">
-        <v>26</v>
+        <v>53</v>
       </c>
       <c r="B281" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="C281" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D281" t="s">
         <v>322</v>
@@ -7722,15 +7735,15 @@
         <v>19</v>
       </c>
       <c r="F281">
-        <v>2017</v>
+        <v>2019</v>
       </c>
     </row>
     <row r="282" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A282" t="s">
-        <v>26</v>
+      <c r="A282">
+        <v>1</v>
       </c>
       <c r="B282" t="s">
-        <v>325</v>
+        <v>531</v>
       </c>
       <c r="C282" t="s">
         <v>13</v>
@@ -7745,52 +7758,12 @@
         <v>2014</v>
       </c>
     </row>
-    <row r="283" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A283" t="s">
-        <v>53</v>
-      </c>
-      <c r="B283" t="s">
-        <v>326</v>
-      </c>
-      <c r="C283" t="s">
-        <v>13</v>
-      </c>
-      <c r="D283" t="s">
-        <v>322</v>
-      </c>
-      <c r="E283" t="s">
-        <v>19</v>
-      </c>
-      <c r="F283">
-        <v>2019</v>
-      </c>
-    </row>
-    <row r="284" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A284">
-        <v>1</v>
-      </c>
-      <c r="B284" t="s">
-        <v>531</v>
-      </c>
-      <c r="C284" t="s">
-        <v>13</v>
-      </c>
-      <c r="D284" t="s">
-        <v>322</v>
-      </c>
-      <c r="E284" t="s">
-        <v>19</v>
-      </c>
-      <c r="F284">
-        <v>2014</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:F271" xr:uid="{1909AEDC-558D-47FF-AACF-A1C78DAFF0D0}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:F283">
-    <sortCondition ref="E2:E283"/>
-    <sortCondition ref="D2:D283"/>
-    <sortCondition ref="C2:C283"/>
+  <autoFilter ref="A1:F282" xr:uid="{1909AEDC-558D-47FF-AACF-A1C78DAFF0D0}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:F282">
+    <sortCondition ref="E2:E282"/>
+    <sortCondition ref="D2:D282"/>
+    <sortCondition ref="C2:C282"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -7798,10 +7771,11 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C4C1D83B-06EB-4933-BDB2-73F3C739F36C}">
-  <dimension ref="A1:N185"/>
+  <dimension ref="A1:N184"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="15.36328125" customWidth="1"/>
+    <col min="10" max="10" width="18.36328125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:14" x14ac:dyDescent="0.35">
@@ -8173,23 +8147,23 @@
       <c r="F11">
         <v>2026</v>
       </c>
-      <c r="I11" t="s">
-        <v>53</v>
+      <c r="I11">
+        <v>1</v>
       </c>
       <c r="J11" t="s">
-        <v>539</v>
+        <v>546</v>
       </c>
       <c r="K11" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="L11" t="s">
-        <v>329</v>
+        <v>322</v>
       </c>
       <c r="M11" t="s">
         <v>19</v>
       </c>
       <c r="N11">
-        <v>2026</v>
+        <v>2024</v>
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.35">
@@ -8211,23 +8185,23 @@
       <c r="F12">
         <v>2022</v>
       </c>
-      <c r="I12">
-        <v>1</v>
+      <c r="I12" t="s">
+        <v>26</v>
       </c>
       <c r="J12" t="s">
-        <v>546</v>
+        <v>347</v>
       </c>
       <c r="K12" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="L12" t="s">
-        <v>322</v>
+        <v>11</v>
       </c>
       <c r="M12" t="s">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="N12">
-        <v>2024</v>
+        <v>2023</v>
       </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.35">
@@ -8249,23 +8223,23 @@
       <c r="F13">
         <v>2026</v>
       </c>
-      <c r="I13" t="s">
-        <v>26</v>
+      <c r="I13">
+        <v>2</v>
       </c>
       <c r="J13" t="s">
-        <v>347</v>
+        <v>111</v>
       </c>
       <c r="K13" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="L13" t="s">
-        <v>11</v>
+        <v>107</v>
       </c>
       <c r="M13" t="s">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="N13">
-        <v>2023</v>
+        <v>2020</v>
       </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.35">
@@ -8291,19 +8265,19 @@
         <v>2</v>
       </c>
       <c r="J14" t="s">
-        <v>111</v>
+        <v>123</v>
       </c>
       <c r="K14" t="s">
         <v>13</v>
       </c>
       <c r="L14" t="s">
-        <v>107</v>
+        <v>117</v>
       </c>
       <c r="M14" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="N14">
-        <v>2020</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.35">
@@ -8325,23 +8299,23 @@
       <c r="F15">
         <v>2023</v>
       </c>
-      <c r="I15">
-        <v>2</v>
+      <c r="I15" t="s">
+        <v>53</v>
       </c>
       <c r="J15" t="s">
-        <v>123</v>
+        <v>133</v>
       </c>
       <c r="K15" t="s">
         <v>13</v>
       </c>
       <c r="L15" t="s">
-        <v>117</v>
+        <v>128</v>
       </c>
       <c r="M15" t="s">
         <v>16</v>
       </c>
       <c r="N15">
-        <v>2025</v>
+        <v>2022</v>
       </c>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.35">
@@ -8363,20 +8337,20 @@
       <c r="F16">
         <v>2025</v>
       </c>
-      <c r="I16" t="s">
-        <v>53</v>
+      <c r="I16">
+        <v>1</v>
       </c>
       <c r="J16" t="s">
-        <v>133</v>
+        <v>170</v>
       </c>
       <c r="K16" t="s">
         <v>13</v>
       </c>
       <c r="L16" t="s">
-        <v>128</v>
+        <v>167</v>
       </c>
       <c r="M16" t="s">
-        <v>16</v>
+        <v>157</v>
       </c>
       <c r="N16">
         <v>2022</v>
@@ -8402,22 +8376,22 @@
         <v>2026</v>
       </c>
       <c r="I17">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J17" t="s">
-        <v>170</v>
+        <v>191</v>
       </c>
       <c r="K17" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L17" t="s">
-        <v>167</v>
+        <v>185</v>
       </c>
       <c r="M17" t="s">
         <v>157</v>
       </c>
       <c r="N17">
-        <v>2022</v>
+        <v>2017</v>
       </c>
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.35">
@@ -8439,23 +8413,23 @@
       <c r="F18">
         <v>2023</v>
       </c>
-      <c r="I18">
-        <v>2</v>
+      <c r="I18" t="s">
+        <v>53</v>
       </c>
       <c r="J18" t="s">
-        <v>191</v>
+        <v>214</v>
       </c>
       <c r="K18" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="L18" t="s">
-        <v>185</v>
+        <v>215</v>
       </c>
       <c r="M18" t="s">
-        <v>157</v>
+        <v>196</v>
       </c>
       <c r="N18">
-        <v>2017</v>
+        <v>2020</v>
       </c>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.35">
@@ -8477,14 +8451,14 @@
       <c r="F19">
         <v>2026</v>
       </c>
-      <c r="I19" t="s">
-        <v>53</v>
+      <c r="I19">
+        <v>1</v>
       </c>
       <c r="J19" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="K19" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="L19" t="s">
         <v>215</v>
@@ -8493,7 +8467,7 @@
         <v>196</v>
       </c>
       <c r="N19">
-        <v>2020</v>
+        <v>2024</v>
       </c>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.35">
@@ -8519,7 +8493,7 @@
         <v>1</v>
       </c>
       <c r="J20" t="s">
-        <v>217</v>
+        <v>451</v>
       </c>
       <c r="K20" t="s">
         <v>12</v>
@@ -8531,7 +8505,7 @@
         <v>196</v>
       </c>
       <c r="N20">
-        <v>2024</v>
+        <v>2023</v>
       </c>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.35">
@@ -8554,22 +8528,22 @@
         <v>2020</v>
       </c>
       <c r="I21">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J21" t="s">
-        <v>451</v>
+        <v>241</v>
       </c>
       <c r="K21" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="L21" t="s">
-        <v>215</v>
+        <v>17</v>
       </c>
       <c r="M21" t="s">
-        <v>196</v>
+        <v>18</v>
       </c>
       <c r="N21">
-        <v>2023</v>
+        <v>2020</v>
       </c>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.35">
@@ -8591,23 +8565,23 @@
       <c r="F22">
         <v>2026</v>
       </c>
-      <c r="I22">
-        <v>2</v>
+      <c r="I22" t="s">
+        <v>26</v>
       </c>
       <c r="J22" t="s">
-        <v>241</v>
+        <v>316</v>
       </c>
       <c r="K22" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="L22" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="M22" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="N22">
-        <v>2020</v>
+        <v>2014</v>
       </c>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.35">
@@ -8629,24 +8603,22 @@
       <c r="F23">
         <v>2024</v>
       </c>
-      <c r="I23" t="s">
-        <v>26</v>
+      <c r="I23">
+        <v>2</v>
       </c>
       <c r="J23" t="s">
-        <v>316</v>
+        <v>547</v>
       </c>
       <c r="K23" t="s">
         <v>13</v>
       </c>
       <c r="L23" t="s">
-        <v>20</v>
+        <v>322</v>
       </c>
       <c r="M23" t="s">
         <v>19</v>
       </c>
-      <c r="N23">
-        <v>2014</v>
-      </c>
+      <c r="N23" s="1"/>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A24">
@@ -8667,6 +8639,24 @@
       <c r="F24">
         <v>2026</v>
       </c>
+      <c r="I24">
+        <v>1</v>
+      </c>
+      <c r="J24" t="s">
+        <v>207</v>
+      </c>
+      <c r="K24" t="s">
+        <v>12</v>
+      </c>
+      <c r="L24" t="s">
+        <v>204</v>
+      </c>
+      <c r="M24" t="s">
+        <v>196</v>
+      </c>
+      <c r="N24">
+        <v>2024</v>
+      </c>
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A25">
@@ -8687,25 +8677,61 @@
       <c r="F25">
         <v>2016</v>
       </c>
+      <c r="I25">
+        <v>1</v>
+      </c>
+      <c r="J25" t="s">
+        <v>450</v>
+      </c>
+      <c r="K25" t="s">
+        <v>12</v>
+      </c>
+      <c r="L25" t="s">
+        <v>215</v>
+      </c>
+      <c r="M25" t="s">
+        <v>196</v>
+      </c>
+      <c r="N25">
+        <v>2022</v>
+      </c>
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A26">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B26" t="s">
-        <v>365</v>
+        <v>83</v>
       </c>
       <c r="C26" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="D26" t="s">
-        <v>87</v>
+        <v>21</v>
       </c>
       <c r="E26" t="s">
         <v>22</v>
       </c>
       <c r="F26">
-        <v>2008</v>
+        <v>2024</v>
+      </c>
+      <c r="I26">
+        <v>2</v>
+      </c>
+      <c r="J26" t="s">
+        <v>226</v>
+      </c>
+      <c r="K26" t="s">
+        <v>12</v>
+      </c>
+      <c r="L26" t="s">
+        <v>225</v>
+      </c>
+      <c r="M26" t="s">
+        <v>196</v>
+      </c>
+      <c r="N26">
+        <v>2025</v>
       </c>
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.35">
@@ -8713,30 +8739,48 @@
         <v>1</v>
       </c>
       <c r="B27" t="s">
-        <v>366</v>
+        <v>82</v>
       </c>
       <c r="C27" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="D27" t="s">
-        <v>87</v>
+        <v>21</v>
       </c>
       <c r="E27" t="s">
         <v>22</v>
       </c>
       <c r="F27">
-        <v>2023</v>
+        <v>2026</v>
+      </c>
+      <c r="I27">
+        <v>1</v>
+      </c>
+      <c r="J27" t="s">
+        <v>468</v>
+      </c>
+      <c r="K27" t="s">
+        <v>12</v>
+      </c>
+      <c r="L27" t="s">
+        <v>243</v>
+      </c>
+      <c r="M27" t="s">
+        <v>18</v>
+      </c>
+      <c r="N27">
+        <v>2022</v>
       </c>
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A28">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B28" t="s">
-        <v>369</v>
+        <v>365</v>
       </c>
       <c r="C28" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="D28" t="s">
         <v>87</v>
@@ -8745,7 +8789,25 @@
         <v>22</v>
       </c>
       <c r="F28">
-        <v>2019</v>
+        <v>2008</v>
+      </c>
+      <c r="I28">
+        <v>1</v>
+      </c>
+      <c r="J28" t="s">
+        <v>70</v>
+      </c>
+      <c r="K28" t="s">
+        <v>13</v>
+      </c>
+      <c r="L28" t="s">
+        <v>10</v>
+      </c>
+      <c r="M28" t="s">
+        <v>6</v>
+      </c>
+      <c r="N28">
+        <v>2017</v>
       </c>
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.35">
@@ -8753,10 +8815,10 @@
         <v>1</v>
       </c>
       <c r="B29" t="s">
-        <v>370</v>
+        <v>366</v>
       </c>
       <c r="C29" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="D29" t="s">
         <v>87</v>
@@ -8765,7 +8827,25 @@
         <v>22</v>
       </c>
       <c r="F29">
-        <v>2024</v>
+        <v>2023</v>
+      </c>
+      <c r="I29">
+        <v>1</v>
+      </c>
+      <c r="J29" t="s">
+        <v>125</v>
+      </c>
+      <c r="K29" t="s">
+        <v>13</v>
+      </c>
+      <c r="L29" t="s">
+        <v>117</v>
+      </c>
+      <c r="M29" t="s">
+        <v>16</v>
+      </c>
+      <c r="N29">
+        <v>2025</v>
       </c>
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.35">
@@ -8773,10 +8853,10 @@
         <v>1</v>
       </c>
       <c r="B30" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="C30" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D30" t="s">
         <v>87</v>
@@ -8785,7 +8865,25 @@
         <v>22</v>
       </c>
       <c r="F30">
-        <v>2023</v>
+        <v>2019</v>
+      </c>
+      <c r="I30" t="s">
+        <v>53</v>
+      </c>
+      <c r="J30" t="s">
+        <v>229</v>
+      </c>
+      <c r="K30" t="s">
+        <v>13</v>
+      </c>
+      <c r="L30" t="s">
+        <v>225</v>
+      </c>
+      <c r="M30" t="s">
+        <v>196</v>
+      </c>
+      <c r="N30">
+        <v>2019</v>
       </c>
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.35">
@@ -8793,10 +8891,10 @@
         <v>1</v>
       </c>
       <c r="B31" t="s">
-        <v>94</v>
+        <v>370</v>
       </c>
       <c r="C31" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D31" t="s">
         <v>87</v>
@@ -8805,7 +8903,7 @@
         <v>22</v>
       </c>
       <c r="F31">
-        <v>2026</v>
+        <v>2024</v>
       </c>
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.35">
@@ -8813,19 +8911,19 @@
         <v>1</v>
       </c>
       <c r="B32" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
       <c r="C32" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="D32" t="s">
-        <v>97</v>
+        <v>87</v>
       </c>
       <c r="E32" t="s">
         <v>22</v>
       </c>
       <c r="F32">
-        <v>2025</v>
+        <v>2023</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.35">
@@ -8833,13 +8931,13 @@
         <v>1</v>
       </c>
       <c r="B33" t="s">
-        <v>372</v>
+        <v>94</v>
       </c>
       <c r="C33" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="D33" t="s">
-        <v>97</v>
+        <v>87</v>
       </c>
       <c r="E33" t="s">
         <v>22</v>
@@ -8853,10 +8951,10 @@
         <v>1</v>
       </c>
       <c r="B34" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="C34" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="D34" t="s">
         <v>97</v>
@@ -8865,7 +8963,7 @@
         <v>22</v>
       </c>
       <c r="F34">
-        <v>2023</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.35">
@@ -8873,10 +8971,10 @@
         <v>1</v>
       </c>
       <c r="B35" t="s">
-        <v>376</v>
+        <v>372</v>
       </c>
       <c r="C35" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="D35" t="s">
         <v>97</v>
@@ -8885,7 +8983,7 @@
         <v>22</v>
       </c>
       <c r="F35">
-        <v>2023</v>
+        <v>2026</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.35">
@@ -8893,10 +8991,10 @@
         <v>1</v>
       </c>
       <c r="B36" t="s">
-        <v>377</v>
+        <v>373</v>
       </c>
       <c r="C36" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D36" t="s">
         <v>97</v>
@@ -8905,7 +9003,7 @@
         <v>22</v>
       </c>
       <c r="F36">
-        <v>2026</v>
+        <v>2023</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.35">
@@ -8913,10 +9011,10 @@
         <v>1</v>
       </c>
       <c r="B37" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="C37" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D37" t="s">
         <v>97</v>
@@ -8925,7 +9023,7 @@
         <v>22</v>
       </c>
       <c r="F37">
-        <v>2024</v>
+        <v>2023</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.35">
@@ -8933,10 +9031,10 @@
         <v>1</v>
       </c>
       <c r="B38" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="C38" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D38" t="s">
         <v>97</v>
@@ -8945,7 +9043,7 @@
         <v>22</v>
       </c>
       <c r="F38">
-        <v>2021</v>
+        <v>2026</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.35">
@@ -8953,19 +9051,19 @@
         <v>1</v>
       </c>
       <c r="B39" t="s">
-        <v>378</v>
+        <v>374</v>
       </c>
       <c r="C39" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="D39" t="s">
-        <v>107</v>
+        <v>97</v>
       </c>
       <c r="E39" t="s">
         <v>22</v>
       </c>
       <c r="F39">
-        <v>2018</v>
+        <v>2024</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.35">
@@ -8973,19 +9071,19 @@
         <v>1</v>
       </c>
       <c r="B40" t="s">
-        <v>379</v>
+        <v>375</v>
       </c>
       <c r="C40" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="D40" t="s">
-        <v>107</v>
+        <v>97</v>
       </c>
       <c r="E40" t="s">
         <v>22</v>
       </c>
       <c r="F40">
-        <v>2025</v>
+        <v>2021</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.35">
@@ -8993,7 +9091,7 @@
         <v>1</v>
       </c>
       <c r="B41" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="C41" t="s">
         <v>7</v>
@@ -9005,7 +9103,7 @@
         <v>22</v>
       </c>
       <c r="F41">
-        <v>2026</v>
+        <v>2018</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.35">
@@ -9013,10 +9111,10 @@
         <v>1</v>
       </c>
       <c r="B42" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="C42" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="D42" t="s">
         <v>107</v>
@@ -9025,7 +9123,7 @@
         <v>22</v>
       </c>
       <c r="F42">
-        <v>2019</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.35">
@@ -9033,10 +9131,10 @@
         <v>1</v>
       </c>
       <c r="B43" t="s">
-        <v>383</v>
+        <v>380</v>
       </c>
       <c r="C43" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="D43" t="s">
         <v>107</v>
@@ -9045,7 +9143,7 @@
         <v>22</v>
       </c>
       <c r="F43">
-        <v>2017</v>
+        <v>2026</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.35">
@@ -9053,10 +9151,10 @@
         <v>1</v>
       </c>
       <c r="B44" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="C44" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D44" t="s">
         <v>107</v>
@@ -9065,7 +9163,7 @@
         <v>22</v>
       </c>
       <c r="F44">
-        <v>2021</v>
+        <v>2019</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.35">
@@ -9073,19 +9171,19 @@
         <v>1</v>
       </c>
       <c r="B45" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="C45" t="s">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="D45" t="s">
-        <v>117</v>
+        <v>107</v>
       </c>
       <c r="E45" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="F45">
-        <v>2021</v>
+        <v>2017</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.35">
@@ -9093,19 +9191,19 @@
         <v>1</v>
       </c>
       <c r="B46" t="s">
-        <v>385</v>
+        <v>382</v>
       </c>
       <c r="C46" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="D46" t="s">
-        <v>117</v>
+        <v>107</v>
       </c>
       <c r="E46" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="F46">
-        <v>2026</v>
+        <v>2021</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.35">
@@ -9113,10 +9211,10 @@
         <v>1</v>
       </c>
       <c r="B47" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="C47" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="D47" t="s">
         <v>117</v>
@@ -9125,7 +9223,7 @@
         <v>16</v>
       </c>
       <c r="F47">
-        <v>2017</v>
+        <v>2021</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.35">
@@ -9133,10 +9231,10 @@
         <v>1</v>
       </c>
       <c r="B48" t="s">
-        <v>390</v>
+        <v>385</v>
       </c>
       <c r="C48" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="D48" t="s">
         <v>117</v>
@@ -9145,7 +9243,7 @@
         <v>16</v>
       </c>
       <c r="F48">
-        <v>2024</v>
+        <v>2026</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.35">
@@ -9153,10 +9251,10 @@
         <v>1</v>
       </c>
       <c r="B49" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="C49" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D49" t="s">
         <v>117</v>
@@ -9165,7 +9263,7 @@
         <v>16</v>
       </c>
       <c r="F49">
-        <v>2023</v>
+        <v>2017</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.35">
@@ -9173,10 +9271,10 @@
         <v>1</v>
       </c>
       <c r="B50" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="C50" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D50" t="s">
         <v>117</v>
@@ -9185,7 +9283,7 @@
         <v>16</v>
       </c>
       <c r="F50">
-        <v>2026</v>
+        <v>2024</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.35">
@@ -9193,13 +9291,13 @@
         <v>1</v>
       </c>
       <c r="B51" t="s">
-        <v>391</v>
+        <v>387</v>
       </c>
       <c r="C51" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="D51" t="s">
-        <v>128</v>
+        <v>117</v>
       </c>
       <c r="E51" t="s">
         <v>16</v>
@@ -9213,19 +9311,19 @@
         <v>1</v>
       </c>
       <c r="B52" t="s">
-        <v>392</v>
+        <v>388</v>
       </c>
       <c r="C52" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="D52" t="s">
-        <v>128</v>
+        <v>117</v>
       </c>
       <c r="E52" t="s">
         <v>16</v>
       </c>
       <c r="F52">
-        <v>2025</v>
+        <v>2026</v>
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.35">
@@ -9233,10 +9331,10 @@
         <v>1</v>
       </c>
       <c r="B53" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="C53" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="D53" t="s">
         <v>128</v>
@@ -9245,7 +9343,7 @@
         <v>16</v>
       </c>
       <c r="F53">
-        <v>2026</v>
+        <v>2023</v>
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.35">
@@ -9253,10 +9351,10 @@
         <v>1</v>
       </c>
       <c r="B54" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="C54" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="D54" t="s">
         <v>128</v>
@@ -9273,10 +9371,10 @@
         <v>1</v>
       </c>
       <c r="B55" t="s">
-        <v>397</v>
+        <v>394</v>
       </c>
       <c r="C55" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D55" t="s">
         <v>128</v>
@@ -9285,7 +9383,7 @@
         <v>16</v>
       </c>
       <c r="F55">
-        <v>2017</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.35">
@@ -9293,7 +9391,7 @@
         <v>1</v>
       </c>
       <c r="B56" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="C56" t="s">
         <v>14</v>
@@ -9305,7 +9403,7 @@
         <v>16</v>
       </c>
       <c r="F56">
-        <v>2022</v>
+        <v>2017</v>
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.35">
@@ -9313,10 +9411,10 @@
         <v>1</v>
       </c>
       <c r="B57" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
       <c r="C57" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D57" t="s">
         <v>128</v>
@@ -9325,7 +9423,7 @@
         <v>16</v>
       </c>
       <c r="F57">
-        <v>2026</v>
+        <v>2022</v>
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.35">
@@ -9333,7 +9431,7 @@
         <v>1</v>
       </c>
       <c r="B58" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="C58" t="s">
         <v>13</v>
@@ -9345,7 +9443,7 @@
         <v>16</v>
       </c>
       <c r="F58">
-        <v>2019</v>
+        <v>2026</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.35">
@@ -9353,19 +9451,19 @@
         <v>1</v>
       </c>
       <c r="B59" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="C59" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="D59" t="s">
-        <v>136</v>
+        <v>128</v>
       </c>
       <c r="E59" t="s">
         <v>16</v>
       </c>
       <c r="F59">
-        <v>2024</v>
+        <v>2019</v>
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.35">
@@ -9373,7 +9471,7 @@
         <v>1</v>
       </c>
       <c r="B60" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="C60" t="s">
         <v>7</v>
@@ -9385,7 +9483,7 @@
         <v>16</v>
       </c>
       <c r="F60">
-        <v>2026</v>
+        <v>2024</v>
       </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.35">
@@ -9393,10 +9491,10 @@
         <v>1</v>
       </c>
       <c r="B61" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="C61" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="D61" t="s">
         <v>136</v>
@@ -9405,7 +9503,7 @@
         <v>16</v>
       </c>
       <c r="F61">
-        <v>2021</v>
+        <v>2026</v>
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.35">
@@ -9413,10 +9511,10 @@
         <v>1</v>
       </c>
       <c r="B62" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="C62" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D62" t="s">
         <v>136</v>
@@ -9425,7 +9523,7 @@
         <v>16</v>
       </c>
       <c r="F62">
-        <v>2026</v>
+        <v>2021</v>
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.35">
@@ -9433,19 +9531,19 @@
         <v>1</v>
       </c>
       <c r="B63" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="C63" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="D63" t="s">
-        <v>15</v>
+        <v>136</v>
       </c>
       <c r="E63" t="s">
         <v>16</v>
       </c>
       <c r="F63">
-        <v>2017</v>
+        <v>2026</v>
       </c>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.35">
@@ -9453,7 +9551,7 @@
         <v>1</v>
       </c>
       <c r="B64" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="C64" t="s">
         <v>7</v>
@@ -9465,7 +9563,7 @@
         <v>16</v>
       </c>
       <c r="F64">
-        <v>2023</v>
+        <v>2017</v>
       </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.35">
@@ -9473,10 +9571,10 @@
         <v>1</v>
       </c>
       <c r="B65" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="C65" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="D65" t="s">
         <v>15</v>
@@ -9485,7 +9583,7 @@
         <v>16</v>
       </c>
       <c r="F65">
-        <v>2022</v>
+        <v>2023</v>
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.35">
@@ -9493,7 +9591,7 @@
         <v>1</v>
       </c>
       <c r="B66" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="C66" t="s">
         <v>14</v>
@@ -9505,7 +9603,7 @@
         <v>16</v>
       </c>
       <c r="F66">
-        <v>2024</v>
+        <v>2022</v>
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.35">
@@ -9513,19 +9611,19 @@
         <v>1</v>
       </c>
       <c r="B67" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="C67" t="s">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="D67" t="s">
-        <v>156</v>
+        <v>15</v>
       </c>
       <c r="E67" t="s">
-        <v>157</v>
+        <v>16</v>
       </c>
       <c r="F67">
-        <v>2019</v>
+        <v>2024</v>
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.35">
@@ -9533,7 +9631,7 @@
         <v>1</v>
       </c>
       <c r="B68" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="C68" t="s">
         <v>7</v>
@@ -9545,7 +9643,7 @@
         <v>157</v>
       </c>
       <c r="F68">
-        <v>2021</v>
+        <v>2019</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.35">
@@ -9553,10 +9651,10 @@
         <v>1</v>
       </c>
       <c r="B69" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="C69" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="D69" t="s">
         <v>156</v>
@@ -9565,7 +9663,7 @@
         <v>157</v>
       </c>
       <c r="F69">
-        <v>2022</v>
+        <v>2021</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.35">
@@ -9573,10 +9671,10 @@
         <v>1</v>
       </c>
       <c r="B70" t="s">
-        <v>412</v>
+        <v>409</v>
       </c>
       <c r="C70" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D70" t="s">
         <v>156</v>
@@ -9585,7 +9683,7 @@
         <v>157</v>
       </c>
       <c r="F70">
-        <v>2020</v>
+        <v>2022</v>
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.35">
@@ -9593,7 +9691,7 @@
         <v>1</v>
       </c>
       <c r="B71" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="C71" t="s">
         <v>14</v>
@@ -9605,7 +9703,7 @@
         <v>157</v>
       </c>
       <c r="F71">
-        <v>2023</v>
+        <v>2020</v>
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.35">
@@ -9613,10 +9711,10 @@
         <v>1</v>
       </c>
       <c r="B72" t="s">
-        <v>410</v>
+        <v>413</v>
       </c>
       <c r="C72" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D72" t="s">
         <v>156</v>
@@ -9625,7 +9723,7 @@
         <v>157</v>
       </c>
       <c r="F72">
-        <v>2019</v>
+        <v>2023</v>
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.35">
@@ -9633,19 +9731,19 @@
         <v>1</v>
       </c>
       <c r="B73" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="C73" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="D73" t="s">
-        <v>167</v>
+        <v>156</v>
       </c>
       <c r="E73" t="s">
         <v>157</v>
       </c>
       <c r="F73">
-        <v>2021</v>
+        <v>2019</v>
       </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.35">
@@ -9653,7 +9751,7 @@
         <v>1</v>
       </c>
       <c r="B74" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="C74" t="s">
         <v>7</v>
@@ -9665,7 +9763,7 @@
         <v>157</v>
       </c>
       <c r="F74">
-        <v>2026</v>
+        <v>2021</v>
       </c>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.35">
@@ -9673,10 +9771,10 @@
         <v>1</v>
       </c>
       <c r="B75" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="C75" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="D75" t="s">
         <v>167</v>
@@ -9685,7 +9783,7 @@
         <v>157</v>
       </c>
       <c r="F75">
-        <v>2025</v>
+        <v>2026</v>
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.35">
@@ -9693,10 +9791,10 @@
         <v>1</v>
       </c>
       <c r="B76" t="s">
-        <v>420</v>
+        <v>416</v>
       </c>
       <c r="C76" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D76" t="s">
         <v>167</v>
@@ -9705,7 +9803,7 @@
         <v>157</v>
       </c>
       <c r="F76">
-        <v>2021</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.35">
@@ -9713,7 +9811,7 @@
         <v>1</v>
       </c>
       <c r="B77" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="C77" t="s">
         <v>14</v>
@@ -9725,7 +9823,7 @@
         <v>157</v>
       </c>
       <c r="F77">
-        <v>2025</v>
+        <v>2021</v>
       </c>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.35">
@@ -9733,10 +9831,10 @@
         <v>1</v>
       </c>
       <c r="B78" t="s">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="C78" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D78" t="s">
         <v>167</v>
@@ -9745,7 +9843,7 @@
         <v>157</v>
       </c>
       <c r="F78">
-        <v>2023</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.35">
@@ -9753,19 +9851,19 @@
         <v>1</v>
       </c>
       <c r="B79" t="s">
-        <v>428</v>
+        <v>418</v>
       </c>
       <c r="C79" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="D79" t="s">
-        <v>185</v>
+        <v>167</v>
       </c>
       <c r="E79" t="s">
         <v>157</v>
       </c>
       <c r="F79">
-        <v>2021</v>
+        <v>2023</v>
       </c>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.35">
@@ -9773,7 +9871,7 @@
         <v>1</v>
       </c>
       <c r="B80" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="C80" t="s">
         <v>7</v>
@@ -9785,7 +9883,7 @@
         <v>157</v>
       </c>
       <c r="F80">
-        <v>2025</v>
+        <v>2021</v>
       </c>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.35">
@@ -9793,10 +9891,10 @@
         <v>1</v>
       </c>
       <c r="B81" t="s">
-        <v>433</v>
+        <v>429</v>
       </c>
       <c r="C81" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="D81" t="s">
         <v>185</v>
@@ -9813,10 +9911,10 @@
         <v>1</v>
       </c>
       <c r="B82" t="s">
-        <v>430</v>
+        <v>433</v>
       </c>
       <c r="C82" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D82" t="s">
         <v>185</v>
@@ -9825,7 +9923,7 @@
         <v>157</v>
       </c>
       <c r="F82">
-        <v>2018</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.35">
@@ -9833,7 +9931,7 @@
         <v>1</v>
       </c>
       <c r="B83" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="C83" t="s">
         <v>13</v>
@@ -9845,7 +9943,7 @@
         <v>157</v>
       </c>
       <c r="F83">
-        <v>2023</v>
+        <v>2018</v>
       </c>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.35">
@@ -9853,19 +9951,19 @@
         <v>1</v>
       </c>
       <c r="B84" t="s">
-        <v>422</v>
+        <v>431</v>
       </c>
       <c r="C84" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="D84" t="s">
-        <v>175</v>
+        <v>185</v>
       </c>
       <c r="E84" t="s">
         <v>157</v>
       </c>
       <c r="F84">
-        <v>2026</v>
+        <v>2023</v>
       </c>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.35">
@@ -9873,7 +9971,7 @@
         <v>1</v>
       </c>
       <c r="B85" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="C85" t="s">
         <v>7</v>
@@ -9885,7 +9983,7 @@
         <v>157</v>
       </c>
       <c r="F85">
-        <v>2023</v>
+        <v>2026</v>
       </c>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.35">
@@ -9893,10 +9991,10 @@
         <v>1</v>
       </c>
       <c r="B86" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="C86" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="D86" t="s">
         <v>175</v>
@@ -9905,7 +10003,7 @@
         <v>157</v>
       </c>
       <c r="F86">
-        <v>2024</v>
+        <v>2023</v>
       </c>
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.35">
@@ -9913,10 +10011,10 @@
         <v>1</v>
       </c>
       <c r="B87" t="s">
-        <v>427</v>
+        <v>424</v>
       </c>
       <c r="C87" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D87" t="s">
         <v>175</v>
@@ -9925,7 +10023,7 @@
         <v>157</v>
       </c>
       <c r="F87">
-        <v>2018</v>
+        <v>2024</v>
       </c>
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.35">
@@ -9933,10 +10031,10 @@
         <v>1</v>
       </c>
       <c r="B88" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="C88" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D88" t="s">
         <v>175</v>
@@ -9945,7 +10043,7 @@
         <v>157</v>
       </c>
       <c r="F88">
-        <v>2026</v>
+        <v>2018</v>
       </c>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.35">
@@ -9953,7 +10051,7 @@
         <v>1</v>
       </c>
       <c r="B89" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="C89" t="s">
         <v>13</v>
@@ -9965,7 +10063,7 @@
         <v>157</v>
       </c>
       <c r="F89">
-        <v>2022</v>
+        <v>2026</v>
       </c>
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.35">
@@ -9973,16 +10071,16 @@
         <v>1</v>
       </c>
       <c r="B90" t="s">
-        <v>434</v>
+        <v>426</v>
       </c>
       <c r="C90" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="D90" t="s">
-        <v>195</v>
+        <v>175</v>
       </c>
       <c r="E90" t="s">
-        <v>196</v>
+        <v>157</v>
       </c>
       <c r="F90">
         <v>2022</v>
@@ -9993,7 +10091,7 @@
         <v>1</v>
       </c>
       <c r="B91" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="C91" t="s">
         <v>7</v>
@@ -10005,7 +10103,7 @@
         <v>196</v>
       </c>
       <c r="F91">
-        <v>2023</v>
+        <v>2022</v>
       </c>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.35">
@@ -10013,10 +10111,10 @@
         <v>1</v>
       </c>
       <c r="B92" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="C92" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="D92" t="s">
         <v>195</v>
@@ -10025,7 +10123,7 @@
         <v>196</v>
       </c>
       <c r="F92">
-        <v>2022</v>
+        <v>2023</v>
       </c>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.35">
@@ -10033,7 +10131,7 @@
         <v>1</v>
       </c>
       <c r="B93" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="C93" t="s">
         <v>12</v>
@@ -10045,7 +10143,7 @@
         <v>196</v>
       </c>
       <c r="F93">
-        <v>2023</v>
+        <v>2022</v>
       </c>
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.35">
@@ -10053,10 +10151,10 @@
         <v>1</v>
       </c>
       <c r="B94" t="s">
-        <v>440</v>
+        <v>437</v>
       </c>
       <c r="C94" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D94" t="s">
         <v>195</v>
@@ -10065,7 +10163,7 @@
         <v>196</v>
       </c>
       <c r="F94">
-        <v>2024</v>
+        <v>2023</v>
       </c>
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.35">
@@ -10073,7 +10171,7 @@
         <v>1</v>
       </c>
       <c r="B95" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="C95" t="s">
         <v>14</v>
@@ -10085,7 +10183,7 @@
         <v>196</v>
       </c>
       <c r="F95">
-        <v>2023</v>
+        <v>2024</v>
       </c>
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.35">
@@ -10093,10 +10191,10 @@
         <v>1</v>
       </c>
       <c r="B96" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="C96" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D96" t="s">
         <v>195</v>
@@ -10105,7 +10203,7 @@
         <v>196</v>
       </c>
       <c r="F96">
-        <v>2026</v>
+        <v>2023</v>
       </c>
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.35">
@@ -10113,7 +10211,7 @@
         <v>1</v>
       </c>
       <c r="B97" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="C97" t="s">
         <v>13</v>
@@ -10125,7 +10223,7 @@
         <v>196</v>
       </c>
       <c r="F97">
-        <v>2023</v>
+        <v>2026</v>
       </c>
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.35">
@@ -10133,13 +10231,13 @@
         <v>1</v>
       </c>
       <c r="B98" t="s">
-        <v>444</v>
+        <v>439</v>
       </c>
       <c r="C98" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="D98" t="s">
-        <v>204</v>
+        <v>195</v>
       </c>
       <c r="E98" t="s">
         <v>196</v>
@@ -10153,7 +10251,7 @@
         <v>1</v>
       </c>
       <c r="B99" t="s">
-        <v>203</v>
+        <v>444</v>
       </c>
       <c r="C99" t="s">
         <v>7</v>
@@ -10165,7 +10263,7 @@
         <v>196</v>
       </c>
       <c r="F99">
-        <v>2015</v>
+        <v>2023</v>
       </c>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.35">
@@ -10173,10 +10271,10 @@
         <v>1</v>
       </c>
       <c r="B100" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="C100" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="D100" t="s">
         <v>204</v>
@@ -10185,7 +10283,7 @@
         <v>196</v>
       </c>
       <c r="F100">
-        <v>2021</v>
+        <v>2015</v>
       </c>
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.35">
@@ -10193,10 +10291,10 @@
         <v>1</v>
       </c>
       <c r="B101" t="s">
-        <v>447</v>
+        <v>206</v>
       </c>
       <c r="C101" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D101" t="s">
         <v>204</v>
@@ -10205,7 +10303,7 @@
         <v>196</v>
       </c>
       <c r="F101">
-        <v>2016</v>
+        <v>2021</v>
       </c>
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.35">
@@ -10213,10 +10311,10 @@
         <v>1</v>
       </c>
       <c r="B102" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="C102" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D102" t="s">
         <v>204</v>
@@ -10225,7 +10323,7 @@
         <v>196</v>
       </c>
       <c r="F102">
-        <v>2023</v>
+        <v>2016</v>
       </c>
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.35">
@@ -10233,7 +10331,7 @@
         <v>1</v>
       </c>
       <c r="B103" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="C103" t="s">
         <v>13</v>
@@ -10253,19 +10351,19 @@
         <v>1</v>
       </c>
       <c r="B104" t="s">
-        <v>449</v>
+        <v>446</v>
       </c>
       <c r="C104" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="D104" t="s">
-        <v>215</v>
+        <v>204</v>
       </c>
       <c r="E104" t="s">
         <v>196</v>
       </c>
       <c r="F104">
-        <v>2026</v>
+        <v>2023</v>
       </c>
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.35">
@@ -10273,10 +10371,10 @@
         <v>1</v>
       </c>
       <c r="B105" t="s">
-        <v>452</v>
+        <v>449</v>
       </c>
       <c r="C105" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="D105" t="s">
         <v>215</v>
@@ -10285,7 +10383,7 @@
         <v>196</v>
       </c>
       <c r="F105">
-        <v>2019</v>
+        <v>2026</v>
       </c>
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.35">
@@ -10293,7 +10391,7 @@
         <v>1</v>
       </c>
       <c r="B106" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="C106" t="s">
         <v>14</v>
@@ -10305,7 +10403,7 @@
         <v>196</v>
       </c>
       <c r="F106">
-        <v>2024</v>
+        <v>2019</v>
       </c>
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.35">
@@ -10313,7 +10411,7 @@
         <v>1</v>
       </c>
       <c r="B107" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="C107" t="s">
         <v>14</v>
@@ -10325,7 +10423,7 @@
         <v>196</v>
       </c>
       <c r="F107">
-        <v>2026</v>
+        <v>2024</v>
       </c>
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.35">
@@ -10333,19 +10431,19 @@
         <v>1</v>
       </c>
       <c r="B108" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="C108" t="s">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="D108" t="s">
-        <v>225</v>
+        <v>215</v>
       </c>
       <c r="E108" t="s">
         <v>196</v>
       </c>
       <c r="F108">
-        <v>2015</v>
+        <v>2026</v>
       </c>
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.35">
@@ -10353,7 +10451,7 @@
         <v>1</v>
       </c>
       <c r="B109" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="C109" t="s">
         <v>7</v>
@@ -10365,7 +10463,7 @@
         <v>196</v>
       </c>
       <c r="F109">
-        <v>2026</v>
+        <v>2015</v>
       </c>
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.35">
@@ -10373,10 +10471,10 @@
         <v>1</v>
       </c>
       <c r="B110" t="s">
-        <v>459</v>
+        <v>456</v>
       </c>
       <c r="C110" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="D110" t="s">
         <v>225</v>
@@ -10385,7 +10483,7 @@
         <v>196</v>
       </c>
       <c r="F110">
-        <v>2021</v>
+        <v>2026</v>
       </c>
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.35">
@@ -10393,7 +10491,7 @@
         <v>1</v>
       </c>
       <c r="B111" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="C111" t="s">
         <v>14</v>
@@ -10405,7 +10503,7 @@
         <v>196</v>
       </c>
       <c r="F111">
-        <v>2024</v>
+        <v>2021</v>
       </c>
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.35">
@@ -10413,10 +10511,10 @@
         <v>1</v>
       </c>
       <c r="B112" t="s">
-        <v>457</v>
+        <v>460</v>
       </c>
       <c r="C112" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D112" t="s">
         <v>225</v>
@@ -10425,7 +10523,7 @@
         <v>196</v>
       </c>
       <c r="F112">
-        <v>2021</v>
+        <v>2024</v>
       </c>
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.35">
@@ -10513,19 +10611,19 @@
         <v>1</v>
       </c>
       <c r="B117" t="s">
-        <v>464</v>
+        <v>240</v>
       </c>
       <c r="C117" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="D117" t="s">
-        <v>243</v>
+        <v>17</v>
       </c>
       <c r="E117" t="s">
         <v>18</v>
       </c>
       <c r="F117">
-        <v>2017</v>
+        <v>2026</v>
       </c>
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.35">
@@ -10533,7 +10631,7 @@
         <v>1</v>
       </c>
       <c r="B118" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="C118" t="s">
         <v>7</v>
@@ -10545,7 +10643,7 @@
         <v>18</v>
       </c>
       <c r="F118">
-        <v>2026</v>
+        <v>2017</v>
       </c>
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.35">
@@ -10553,10 +10651,10 @@
         <v>1</v>
       </c>
       <c r="B119" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="C119" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="D119" t="s">
         <v>243</v>
@@ -10565,7 +10663,7 @@
         <v>18</v>
       </c>
       <c r="F119">
-        <v>2024</v>
+        <v>2026</v>
       </c>
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.35">
@@ -10593,10 +10691,10 @@
         <v>1</v>
       </c>
       <c r="B121" t="s">
-        <v>468</v>
+        <v>471</v>
       </c>
       <c r="C121" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D121" t="s">
         <v>243</v>
@@ -10605,7 +10703,7 @@
         <v>18</v>
       </c>
       <c r="F121">
-        <v>2022</v>
+        <v>2021</v>
       </c>
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.35">
@@ -10613,7 +10711,7 @@
         <v>1</v>
       </c>
       <c r="B122" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="C122" t="s">
         <v>14</v>
@@ -10625,7 +10723,7 @@
         <v>18</v>
       </c>
       <c r="F122">
-        <v>2021</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.35">
@@ -10633,10 +10731,10 @@
         <v>1</v>
       </c>
       <c r="B123" t="s">
-        <v>472</v>
+        <v>469</v>
       </c>
       <c r="C123" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D123" t="s">
         <v>243</v>
@@ -10645,7 +10743,7 @@
         <v>18</v>
       </c>
       <c r="F123">
-        <v>2025</v>
+        <v>2022</v>
       </c>
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.35">
@@ -10653,7 +10751,7 @@
         <v>1</v>
       </c>
       <c r="B124" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="C124" t="s">
         <v>13</v>
@@ -10665,7 +10763,7 @@
         <v>18</v>
       </c>
       <c r="F124">
-        <v>2022</v>
+        <v>2019</v>
       </c>
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.35">
@@ -10673,19 +10771,19 @@
         <v>1</v>
       </c>
       <c r="B125" t="s">
-        <v>470</v>
+        <v>473</v>
       </c>
       <c r="C125" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="D125" t="s">
-        <v>243</v>
+        <v>250</v>
       </c>
       <c r="E125" t="s">
         <v>18</v>
       </c>
       <c r="F125">
-        <v>2019</v>
+        <v>2011</v>
       </c>
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.35">
@@ -10693,7 +10791,7 @@
         <v>1</v>
       </c>
       <c r="B126" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="C126" t="s">
         <v>7</v>
@@ -10705,7 +10803,7 @@
         <v>18</v>
       </c>
       <c r="F126">
-        <v>2011</v>
+        <v>2024</v>
       </c>
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.35">
@@ -10713,10 +10811,10 @@
         <v>1</v>
       </c>
       <c r="B127" t="s">
-        <v>474</v>
+        <v>252</v>
       </c>
       <c r="C127" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="D127" t="s">
         <v>250</v>
@@ -10725,7 +10823,7 @@
         <v>18</v>
       </c>
       <c r="F127">
-        <v>2024</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.35">
@@ -10733,10 +10831,10 @@
         <v>1</v>
       </c>
       <c r="B128" t="s">
-        <v>252</v>
+        <v>479</v>
       </c>
       <c r="C128" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D128" t="s">
         <v>250</v>
@@ -10753,10 +10851,10 @@
         <v>1</v>
       </c>
       <c r="B129" t="s">
-        <v>479</v>
+        <v>476</v>
       </c>
       <c r="C129" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D129" t="s">
         <v>250</v>
@@ -10765,7 +10863,7 @@
         <v>18</v>
       </c>
       <c r="F129">
-        <v>2025</v>
+        <v>2026</v>
       </c>
     </row>
     <row r="130" spans="1:6" x14ac:dyDescent="0.35">
@@ -10773,7 +10871,7 @@
         <v>1</v>
       </c>
       <c r="B130" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="C130" t="s">
         <v>13</v>
@@ -10785,7 +10883,7 @@
         <v>18</v>
       </c>
       <c r="F130">
-        <v>2026</v>
+        <v>2022</v>
       </c>
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.35">
@@ -10793,19 +10891,19 @@
         <v>1</v>
       </c>
       <c r="B131" t="s">
-        <v>477</v>
+        <v>480</v>
       </c>
       <c r="C131" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="D131" t="s">
-        <v>250</v>
+        <v>260</v>
       </c>
       <c r="E131" t="s">
         <v>18</v>
       </c>
       <c r="F131">
-        <v>2022</v>
+        <v>2016</v>
       </c>
     </row>
     <row r="132" spans="1:6" x14ac:dyDescent="0.35">
@@ -10813,7 +10911,7 @@
         <v>1</v>
       </c>
       <c r="B132" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="C132" t="s">
         <v>7</v>
@@ -10825,7 +10923,7 @@
         <v>18</v>
       </c>
       <c r="F132">
-        <v>2016</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.35">
@@ -10833,10 +10931,10 @@
         <v>1</v>
       </c>
       <c r="B133" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="C133" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="D133" t="s">
         <v>260</v>
@@ -10845,7 +10943,7 @@
         <v>18</v>
       </c>
       <c r="F133">
-        <v>2025</v>
+        <v>2020</v>
       </c>
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.35">
@@ -10853,7 +10951,7 @@
         <v>1</v>
       </c>
       <c r="B134" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="C134" t="s">
         <v>12</v>
@@ -10865,7 +10963,7 @@
         <v>18</v>
       </c>
       <c r="F134">
-        <v>2020</v>
+        <v>2026</v>
       </c>
     </row>
     <row r="135" spans="1:6" x14ac:dyDescent="0.35">
@@ -10873,10 +10971,10 @@
         <v>1</v>
       </c>
       <c r="B135" t="s">
-        <v>483</v>
+        <v>487</v>
       </c>
       <c r="C135" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D135" t="s">
         <v>260</v>
@@ -10885,7 +10983,7 @@
         <v>18</v>
       </c>
       <c r="F135">
-        <v>2026</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.35">
@@ -10893,7 +10991,7 @@
         <v>1</v>
       </c>
       <c r="B136" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="C136" t="s">
         <v>14</v>
@@ -10905,7 +11003,7 @@
         <v>18</v>
       </c>
       <c r="F136">
-        <v>2025</v>
+        <v>2024</v>
       </c>
     </row>
     <row r="137" spans="1:6" x14ac:dyDescent="0.35">
@@ -10913,10 +11011,10 @@
         <v>1</v>
       </c>
       <c r="B137" t="s">
-        <v>488</v>
+        <v>485</v>
       </c>
       <c r="C137" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D137" t="s">
         <v>260</v>
@@ -10925,15 +11023,15 @@
         <v>18</v>
       </c>
       <c r="F137">
-        <v>2024</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="138" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A138">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B138" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="C138" t="s">
         <v>13</v>
@@ -10945,27 +11043,27 @@
         <v>18</v>
       </c>
       <c r="F138">
-        <v>2025</v>
+        <v>2014</v>
       </c>
     </row>
     <row r="139" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A139">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B139" t="s">
-        <v>486</v>
+        <v>489</v>
       </c>
       <c r="C139" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="D139" t="s">
-        <v>260</v>
+        <v>268</v>
       </c>
       <c r="E139" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="F139">
-        <v>2014</v>
+        <v>2020</v>
       </c>
     </row>
     <row r="140" spans="1:6" x14ac:dyDescent="0.35">
@@ -10973,7 +11071,7 @@
         <v>1</v>
       </c>
       <c r="B140" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="C140" t="s">
         <v>7</v>
@@ -10985,7 +11083,7 @@
         <v>24</v>
       </c>
       <c r="F140">
-        <v>2020</v>
+        <v>2017</v>
       </c>
     </row>
     <row r="141" spans="1:6" x14ac:dyDescent="0.35">
@@ -10993,7 +11091,7 @@
         <v>1</v>
       </c>
       <c r="B141" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="C141" t="s">
         <v>7</v>
@@ -11005,7 +11103,7 @@
         <v>24</v>
       </c>
       <c r="F141">
-        <v>2017</v>
+        <v>2026</v>
       </c>
     </row>
     <row r="142" spans="1:6" x14ac:dyDescent="0.35">
@@ -11013,10 +11111,10 @@
         <v>1</v>
       </c>
       <c r="B142" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="C142" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="D142" t="s">
         <v>268</v>
@@ -11025,7 +11123,7 @@
         <v>24</v>
       </c>
       <c r="F142">
-        <v>2026</v>
+        <v>2021</v>
       </c>
     </row>
     <row r="143" spans="1:6" x14ac:dyDescent="0.35">
@@ -11033,10 +11131,10 @@
         <v>1</v>
       </c>
       <c r="B143" t="s">
-        <v>492</v>
+        <v>495</v>
       </c>
       <c r="C143" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D143" t="s">
         <v>268</v>
@@ -11045,7 +11143,7 @@
         <v>24</v>
       </c>
       <c r="F143">
-        <v>2021</v>
+        <v>2020</v>
       </c>
     </row>
     <row r="144" spans="1:6" x14ac:dyDescent="0.35">
@@ -11053,10 +11151,10 @@
         <v>1</v>
       </c>
       <c r="B144" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="C144" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D144" t="s">
         <v>268</v>
@@ -11065,7 +11163,7 @@
         <v>24</v>
       </c>
       <c r="F144">
-        <v>2020</v>
+        <v>2019</v>
       </c>
     </row>
     <row r="145" spans="1:6" x14ac:dyDescent="0.35">
@@ -11073,7 +11171,7 @@
         <v>1</v>
       </c>
       <c r="B145" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="C145" t="s">
         <v>13</v>
@@ -11085,7 +11183,7 @@
         <v>24</v>
       </c>
       <c r="F145">
-        <v>2019</v>
+        <v>2020</v>
       </c>
     </row>
     <row r="146" spans="1:6" x14ac:dyDescent="0.35">
@@ -11093,19 +11191,19 @@
         <v>1</v>
       </c>
       <c r="B146" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="C146" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="D146" t="s">
-        <v>268</v>
+        <v>277</v>
       </c>
       <c r="E146" t="s">
         <v>24</v>
       </c>
       <c r="F146">
-        <v>2020</v>
+        <v>2022</v>
       </c>
     </row>
     <row r="147" spans="1:6" x14ac:dyDescent="0.35">
@@ -11113,7 +11211,7 @@
         <v>1</v>
       </c>
       <c r="B147" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="C147" t="s">
         <v>7</v>
@@ -11125,7 +11223,7 @@
         <v>24</v>
       </c>
       <c r="F147">
-        <v>2022</v>
+        <v>2026</v>
       </c>
     </row>
     <row r="148" spans="1:6" x14ac:dyDescent="0.35">
@@ -11133,10 +11231,10 @@
         <v>1</v>
       </c>
       <c r="B148" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="C148" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="D148" t="s">
         <v>277</v>
@@ -11145,7 +11243,7 @@
         <v>24</v>
       </c>
       <c r="F148">
-        <v>2026</v>
+        <v>2018</v>
       </c>
     </row>
     <row r="149" spans="1:6" x14ac:dyDescent="0.35">
@@ -11153,7 +11251,7 @@
         <v>1</v>
       </c>
       <c r="B149" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="C149" t="s">
         <v>12</v>
@@ -11165,7 +11263,7 @@
         <v>24</v>
       </c>
       <c r="F149">
-        <v>2018</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="150" spans="1:6" x14ac:dyDescent="0.35">
@@ -11173,10 +11271,10 @@
         <v>1</v>
       </c>
       <c r="B150" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="C150" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D150" t="s">
         <v>277</v>
@@ -11185,7 +11283,7 @@
         <v>24</v>
       </c>
       <c r="F150">
-        <v>2025</v>
+        <v>2017</v>
       </c>
     </row>
     <row r="151" spans="1:6" x14ac:dyDescent="0.35">
@@ -11193,19 +11291,19 @@
         <v>1</v>
       </c>
       <c r="B151" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="C151" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="D151" t="s">
-        <v>277</v>
+        <v>23</v>
       </c>
       <c r="E151" t="s">
         <v>24</v>
       </c>
       <c r="F151">
-        <v>2017</v>
+        <v>2024</v>
       </c>
     </row>
     <row r="152" spans="1:6" x14ac:dyDescent="0.35">
@@ -11213,7 +11311,7 @@
         <v>1</v>
       </c>
       <c r="B152" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="C152" t="s">
         <v>7</v>
@@ -11225,7 +11323,7 @@
         <v>24</v>
       </c>
       <c r="F152">
-        <v>2024</v>
+        <v>2021</v>
       </c>
     </row>
     <row r="153" spans="1:6" x14ac:dyDescent="0.35">
@@ -11233,10 +11331,10 @@
         <v>1</v>
       </c>
       <c r="B153" t="s">
-        <v>503</v>
+        <v>508</v>
       </c>
       <c r="C153" t="s">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="D153" t="s">
         <v>23</v>
@@ -11245,7 +11343,7 @@
         <v>24</v>
       </c>
       <c r="F153">
-        <v>2021</v>
+        <v>2026</v>
       </c>
     </row>
     <row r="154" spans="1:6" x14ac:dyDescent="0.35">
@@ -11253,10 +11351,10 @@
         <v>1</v>
       </c>
       <c r="B154" t="s">
-        <v>508</v>
+        <v>505</v>
       </c>
       <c r="C154" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D154" t="s">
         <v>23</v>
@@ -11265,7 +11363,7 @@
         <v>24</v>
       </c>
       <c r="F154">
-        <v>2026</v>
+        <v>2022</v>
       </c>
     </row>
     <row r="155" spans="1:6" x14ac:dyDescent="0.35">
@@ -11273,7 +11371,7 @@
         <v>1</v>
       </c>
       <c r="B155" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="C155" t="s">
         <v>13</v>
@@ -11285,7 +11383,7 @@
         <v>24</v>
       </c>
       <c r="F155">
-        <v>2022</v>
+        <v>2026</v>
       </c>
     </row>
     <row r="156" spans="1:6" x14ac:dyDescent="0.35">
@@ -11293,19 +11391,19 @@
         <v>1</v>
       </c>
       <c r="B156" t="s">
-        <v>506</v>
+        <v>510</v>
       </c>
       <c r="C156" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="D156" t="s">
-        <v>23</v>
+        <v>296</v>
       </c>
       <c r="E156" t="s">
         <v>24</v>
       </c>
       <c r="F156">
-        <v>2026</v>
+        <v>2019</v>
       </c>
     </row>
     <row r="157" spans="1:6" x14ac:dyDescent="0.35">
@@ -11313,7 +11411,7 @@
         <v>1</v>
       </c>
       <c r="B157" t="s">
-        <v>510</v>
+        <v>295</v>
       </c>
       <c r="C157" t="s">
         <v>7</v>
@@ -11325,7 +11423,7 @@
         <v>24</v>
       </c>
       <c r="F157">
-        <v>2019</v>
+        <v>2026</v>
       </c>
     </row>
     <row r="158" spans="1:6" x14ac:dyDescent="0.35">
@@ -11333,10 +11431,10 @@
         <v>1</v>
       </c>
       <c r="B158" t="s">
-        <v>295</v>
+        <v>513</v>
       </c>
       <c r="C158" t="s">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="D158" t="s">
         <v>296</v>
@@ -11345,7 +11443,7 @@
         <v>24</v>
       </c>
       <c r="F158">
-        <v>2026</v>
+        <v>2023</v>
       </c>
     </row>
     <row r="159" spans="1:6" x14ac:dyDescent="0.35">
@@ -11353,7 +11451,7 @@
         <v>1</v>
       </c>
       <c r="B159" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="C159" t="s">
         <v>14</v>
@@ -11365,7 +11463,7 @@
         <v>24</v>
       </c>
       <c r="F159">
-        <v>2023</v>
+        <v>2026</v>
       </c>
     </row>
     <row r="160" spans="1:6" x14ac:dyDescent="0.35">
@@ -11373,10 +11471,10 @@
         <v>1</v>
       </c>
       <c r="B160" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
       <c r="C160" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D160" t="s">
         <v>296</v>
@@ -11385,7 +11483,7 @@
         <v>24</v>
       </c>
       <c r="F160">
-        <v>2026</v>
+        <v>2024</v>
       </c>
     </row>
     <row r="161" spans="1:6" x14ac:dyDescent="0.35">
@@ -11393,7 +11491,7 @@
         <v>1</v>
       </c>
       <c r="B161" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="C161" t="s">
         <v>13</v>
@@ -11413,19 +11511,19 @@
         <v>1</v>
       </c>
       <c r="B162" t="s">
-        <v>512</v>
+        <v>515</v>
       </c>
       <c r="C162" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="D162" t="s">
-        <v>296</v>
+        <v>306</v>
       </c>
       <c r="E162" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="F162">
-        <v>2024</v>
+        <v>2019</v>
       </c>
     </row>
     <row r="163" spans="1:6" x14ac:dyDescent="0.35">
@@ -11433,7 +11531,7 @@
         <v>1</v>
       </c>
       <c r="B163" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="C163" t="s">
         <v>7</v>
@@ -11445,7 +11543,7 @@
         <v>19</v>
       </c>
       <c r="F163">
-        <v>2019</v>
+        <v>2026</v>
       </c>
     </row>
     <row r="164" spans="1:6" x14ac:dyDescent="0.35">
@@ -11453,10 +11551,10 @@
         <v>1</v>
       </c>
       <c r="B164" t="s">
-        <v>516</v>
+        <v>520</v>
       </c>
       <c r="C164" t="s">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="D164" t="s">
         <v>306</v>
@@ -11465,7 +11563,7 @@
         <v>19</v>
       </c>
       <c r="F164">
-        <v>2026</v>
+        <v>2022</v>
       </c>
     </row>
     <row r="165" spans="1:6" x14ac:dyDescent="0.35">
@@ -11473,10 +11571,10 @@
         <v>1</v>
       </c>
       <c r="B165" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="C165" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D165" t="s">
         <v>306</v>
@@ -11485,7 +11583,7 @@
         <v>19</v>
       </c>
       <c r="F165">
-        <v>2022</v>
+        <v>2023</v>
       </c>
     </row>
     <row r="166" spans="1:6" x14ac:dyDescent="0.35">
@@ -11493,7 +11591,7 @@
         <v>1</v>
       </c>
       <c r="B166" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="C166" t="s">
         <v>13</v>
@@ -11505,7 +11603,7 @@
         <v>19</v>
       </c>
       <c r="F166">
-        <v>2023</v>
+        <v>2021</v>
       </c>
     </row>
     <row r="167" spans="1:6" x14ac:dyDescent="0.35">
@@ -11513,19 +11611,19 @@
         <v>1</v>
       </c>
       <c r="B167" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="C167" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="D167" t="s">
-        <v>306</v>
+        <v>20</v>
       </c>
       <c r="E167" t="s">
         <v>19</v>
       </c>
       <c r="F167">
-        <v>2021</v>
+        <v>2023</v>
       </c>
     </row>
     <row r="168" spans="1:6" x14ac:dyDescent="0.35">
@@ -11533,7 +11631,7 @@
         <v>1</v>
       </c>
       <c r="B168" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="C168" t="s">
         <v>7</v>
@@ -11545,7 +11643,7 @@
         <v>19</v>
       </c>
       <c r="F168">
-        <v>2023</v>
+        <v>2026</v>
       </c>
     </row>
     <row r="169" spans="1:6" x14ac:dyDescent="0.35">
@@ -11553,10 +11651,10 @@
         <v>1</v>
       </c>
       <c r="B169" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="C169" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="D169" t="s">
         <v>20</v>
@@ -11573,10 +11671,10 @@
         <v>1</v>
       </c>
       <c r="B170" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="C170" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D170" t="s">
         <v>20</v>
@@ -11585,7 +11683,7 @@
         <v>19</v>
       </c>
       <c r="F170">
-        <v>2026</v>
+        <v>2023</v>
       </c>
     </row>
     <row r="171" spans="1:6" x14ac:dyDescent="0.35">
@@ -11593,10 +11691,10 @@
         <v>1</v>
       </c>
       <c r="B171" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="C171" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D171" t="s">
         <v>20</v>
@@ -11605,35 +11703,35 @@
         <v>19</v>
       </c>
       <c r="F171">
-        <v>2023</v>
+        <v>2024</v>
       </c>
     </row>
     <row r="172" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A172">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B172" t="s">
-        <v>524</v>
+        <v>536</v>
       </c>
       <c r="C172" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="D172" t="s">
-        <v>20</v>
+        <v>329</v>
       </c>
       <c r="E172" t="s">
         <v>19</v>
       </c>
       <c r="F172">
-        <v>2024</v>
+        <v>2019</v>
       </c>
     </row>
     <row r="173" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A173">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B173" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="C173" t="s">
         <v>7</v>
@@ -11645,7 +11743,7 @@
         <v>19</v>
       </c>
       <c r="F173">
-        <v>2019</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="174" spans="1:6" x14ac:dyDescent="0.35">
@@ -11653,10 +11751,10 @@
         <v>1</v>
       </c>
       <c r="B174" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="C174" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="D174" t="s">
         <v>329</v>
@@ -11665,7 +11763,7 @@
         <v>19</v>
       </c>
       <c r="F174">
-        <v>2025</v>
+        <v>2026</v>
       </c>
     </row>
     <row r="175" spans="1:6" x14ac:dyDescent="0.35">
@@ -11673,10 +11771,10 @@
         <v>1</v>
       </c>
       <c r="B175" t="s">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="C175" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D175" t="s">
         <v>329</v>
@@ -11685,7 +11783,7 @@
         <v>19</v>
       </c>
       <c r="F175">
-        <v>2026</v>
+        <v>2017</v>
       </c>
     </row>
     <row r="176" spans="1:6" x14ac:dyDescent="0.35">
@@ -11693,7 +11791,7 @@
         <v>1</v>
       </c>
       <c r="B176" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="C176" t="s">
         <v>14</v>
@@ -11705,7 +11803,7 @@
         <v>19</v>
       </c>
       <c r="F176">
-        <v>2017</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="177" spans="1:6" x14ac:dyDescent="0.35">
@@ -11713,10 +11811,10 @@
         <v>1</v>
       </c>
       <c r="B177" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="C177" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D177" t="s">
         <v>329</v>
@@ -11733,19 +11831,19 @@
         <v>1</v>
       </c>
       <c r="B178" t="s">
-        <v>542</v>
+        <v>527</v>
       </c>
       <c r="C178" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="D178" t="s">
-        <v>329</v>
+        <v>322</v>
       </c>
       <c r="E178" t="s">
         <v>19</v>
       </c>
       <c r="F178">
-        <v>2025</v>
+        <v>2021</v>
       </c>
     </row>
     <row r="179" spans="1:6" x14ac:dyDescent="0.35">
@@ -11753,7 +11851,7 @@
         <v>1</v>
       </c>
       <c r="B179" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="C179" t="s">
         <v>7</v>
@@ -11765,7 +11863,7 @@
         <v>19</v>
       </c>
       <c r="F179">
-        <v>2021</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="180" spans="1:6" x14ac:dyDescent="0.35">
@@ -11773,10 +11871,10 @@
         <v>1</v>
       </c>
       <c r="B180" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="C180" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="D180" t="s">
         <v>322</v>
@@ -11793,10 +11891,10 @@
         <v>1</v>
       </c>
       <c r="B181" t="s">
-        <v>529</v>
+        <v>534</v>
       </c>
       <c r="C181" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D181" t="s">
         <v>322</v>
@@ -11805,7 +11903,7 @@
         <v>19</v>
       </c>
       <c r="F181">
-        <v>2025</v>
+        <v>2021</v>
       </c>
     </row>
     <row r="182" spans="1:6" x14ac:dyDescent="0.35">
@@ -11813,7 +11911,7 @@
         <v>1</v>
       </c>
       <c r="B182" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="C182" t="s">
         <v>14</v>
@@ -11825,7 +11923,7 @@
         <v>19</v>
       </c>
       <c r="F182">
-        <v>2021</v>
+        <v>2023</v>
       </c>
     </row>
     <row r="183" spans="1:6" x14ac:dyDescent="0.35">
@@ -11833,10 +11931,10 @@
         <v>1</v>
       </c>
       <c r="B183" t="s">
-        <v>535</v>
+        <v>530</v>
       </c>
       <c r="C183" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D183" t="s">
         <v>322</v>
@@ -11845,7 +11943,7 @@
         <v>19</v>
       </c>
       <c r="F183">
-        <v>2023</v>
+        <v>2024</v>
       </c>
     </row>
     <row r="184" spans="1:6" x14ac:dyDescent="0.35">
@@ -11853,7 +11951,7 @@
         <v>1</v>
       </c>
       <c r="B184" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="C184" t="s">
         <v>13</v>
@@ -11865,34 +11963,14 @@
         <v>19</v>
       </c>
       <c r="F184">
-        <v>2024</v>
-      </c>
-    </row>
-    <row r="185" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A185">
-        <v>1</v>
-      </c>
-      <c r="B185" t="s">
-        <v>532</v>
-      </c>
-      <c r="C185" t="s">
-        <v>13</v>
-      </c>
-      <c r="D185" t="s">
-        <v>322</v>
-      </c>
-      <c r="E185" t="s">
-        <v>19</v>
-      </c>
-      <c r="F185">
         <v>2025</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:F185">
-    <sortCondition ref="E3:E185"/>
-    <sortCondition ref="D3:D185"/>
-    <sortCondition ref="C3:C185"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:F184">
+    <sortCondition ref="E3:E184"/>
+    <sortCondition ref="D3:D184"/>
+    <sortCondition ref="C3:C184"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
